--- a/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
@@ -1591,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM29"/>
+  <dimension ref="A1:AR29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.85546875" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2225,31 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
+          <t>Severity (S)</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Severity Note</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Occurrence (O)</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Detection (D)</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Prevention</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>Remark</t>
         </is>
       </c>
@@ -2425,19 +2450,28 @@
       <c r="AC18" s="45" t="n"/>
       <c r="AD18" s="45" t="n"/>
       <c r="AF18" s="45" t="n"/>
-      <c r="AI18" s="45" t="n">
-        <v>8</v>
-      </c>
+      <c r="AI18" s="45" t="n"/>
       <c r="AJ18" s="45" t="n"/>
       <c r="AK18" s="45" t="n"/>
-      <c r="AL18" s="35" t="inlineStr">
+      <c r="AL18" s="35" t="n"/>
+      <c r="AM18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>The End User effects list functional outcomes (no light or dim light) without any explicit safety or regulatory language; given the merged "scratch/damage" mode, the DAMAGE sub-mode can directly cause either total loss or degradation of the headlamp’s primary function, so the worst-case applicable definition is loss of primary function (8).</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>Add a mandatory barcode scan at the sequencing trolley that interlocks the station and blocks tool enable if the scanned headlamp PN/variant does not match the vehicle build sheet, preventing wrong-part selection/mix-up.</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Merged failure mode: 1. Scratch on head lamp; 2. Damage on head lamp. Cause/Mode mismatch: This Cause (wrong part/mix-up) does not physically produce a scratch/damage; it reads like the cause for installing the wrong headlamp variant rather than for scratching/damaging the part. Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended.</t>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Merged failure mode: 1. Scratch on head lamp; 2. Damage on head lamp. Cause/Mode mismatch: This Cause (wrong part/mix-up) does not physically produce a scratch/damage; it reads like the cause for installing the wrong headlamp variant rather than for scratching/damaging the part. Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: FITMENT IS NOT FIRM
+ WRONG SELECTION OF HEAD LAMP
+( NOT AS PER MODEL). Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>
@@ -2523,19 +2557,26 @@
       <c r="AC20" s="45" t="n"/>
       <c r="AD20" s="45" t="n"/>
       <c r="AF20" s="45" t="n"/>
-      <c r="AI20" s="45" t="n">
-        <v>8</v>
-      </c>
+      <c r="AI20" s="45" t="n"/>
       <c r="AJ20" s="45" t="n"/>
       <c r="AK20" s="45" t="n"/>
-      <c r="AL20" s="35" t="inlineStr">
+      <c r="AL20" s="35" t="n"/>
+      <c r="AM20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>The End User effects list either a total loss of the headlamp function ('does not turn ON') or a degraded primary function ('dim light'), both directly plausible from wrong-part selection/mix-up; no safety or regulatory wording is stated. Per the table, these correspond to S=8 or S=7 respectively, with the row-level score set to the higher (8) due to merged/ambiguous mode effects.</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>Add a scan-and-verify lockout at the pick/scan step so the headlamp barcode must match the vehicle’s model code and the line prevents installation if a wrong part is scanned.</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Merged failure mode: 1. Fitment is not firm; 2. Wrong selection of head lamp (not as per model). Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended.</t>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Merged failure mode: 1. Fitment is not firm; 2. Wrong selection of head lamp (not as per model). Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>
@@ -2637,17 +2678,24 @@
       <c r="AC22" s="45" t="n"/>
       <c r="AD22" s="45" t="n"/>
       <c r="AF22" s="45" t="n"/>
-      <c r="AI22" s="45" t="n">
-        <v>10</v>
-      </c>
+      <c r="AI22" s="45" t="n"/>
       <c r="AJ22" s="45" t="n"/>
       <c r="AK22" s="45" t="n"/>
-      <c r="AL22" s="35" t="inlineStr">
+      <c r="AL22" s="35" t="n"/>
+      <c r="AM22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>The End User effect list explicitly states 'Increased risk of accident', which is a plausible consequence of the headlamp not turning on or reduced visibility caused by improper/poor connector locking. Per the table, this affects safe operation of the vehicle, so Severity is 10.</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>Add a poka‑yoke for the headlamp connectors: a latch‑engagement sensor or pull‑back test with line interlock that prevents process completion if the connector is not fully seated and locked.</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. IMPROPER LOCKING; 2. POOR LOCKING. AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
@@ -2761,17 +2809,24 @@
       <c r="AF24" s="12" t="n"/>
       <c r="AG24" s="13" t="n"/>
       <c r="AH24" s="13" t="n"/>
-      <c r="AI24" s="12" t="n">
-        <v>10</v>
-      </c>
+      <c r="AI24" s="12" t="n"/>
       <c r="AJ24" s="12" t="n"/>
       <c r="AK24" s="12" t="n"/>
-      <c r="AL24" s="10" t="inlineStr">
+      <c r="AL24" s="10" t="n"/>
+      <c r="AM24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>The End User effect explicitly states 'Increased risk of accident,' which is a direct and plausible consequence of a headlamp installed without required prefit bolts causing misalignment or compromised illumination. Per the Severity table, this affects safe operation of the vehicle, warranting a 10.</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>Install a DC torque tool with bolt-count and torque OK interlock that prevents station completion unless all headlamp bolts are started and torqued to 6 Nm per the SOS.</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
@@ -2881,17 +2936,24 @@
       <c r="AF26" s="12" t="n"/>
       <c r="AG26" s="13" t="n"/>
       <c r="AH26" s="13" t="n"/>
-      <c r="AI26" s="12" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI26" s="12" t="n"/>
       <c r="AJ26" s="12" t="n"/>
       <c r="AK26" s="12" t="n"/>
-      <c r="AL26" s="10" t="inlineStr">
+      <c r="AL26" s="10" t="n"/>
+      <c r="AM26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>Among the listed End User effects, the only direct outcome of 'failed to fit screws/not maintained gap' is 'rattling or vibration noise during driving', which falls under very objectionable sound/vibration. The more severe-sounding effects (lens crack, bulb burnout, water ingress) require additional unstated failures and are therefore indirect for this mode/cause.</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>Add an in-station fixture with hard locators and an interlocked gap/fastener verification (camera or go/no-go gauge plus screw-counting torque tool) that blocks OK-to-ship unless uniform gaps are met and all screws are installed/torqued.</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. Failed to fit screws; 2. Not maintained gap. Cause/Mode mismatch: The stated Cause addresses only non-uniform gaps to the fender; it does not explain the 'failed to fit screws' portion of the Failure Mode.</t>
         </is>
@@ -3008,19 +3070,26 @@
       <c r="AC28" s="12" t="n"/>
       <c r="AD28" s="12" t="n"/>
       <c r="AF28" s="12" t="n"/>
-      <c r="AI28" s="12" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI28" s="12" t="n"/>
       <c r="AJ28" s="12" t="n"/>
       <c r="AK28" s="12" t="n"/>
-      <c r="AL28" s="10" t="inlineStr">
+      <c r="AL28" s="10" t="n"/>
+      <c r="AM28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>The direct customer-facing outcome of an under-torqued headlamp mount is rattle/vibration noise while driving, which fits the table’s NVH category. This is reasonably treated as very objectionable NVH, aligning with Severity 4.</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>Install a torque-controlled, calibrated electric driver programmed to 6 Nm with OK/NOK lockout to prevent under-torque from operator mistake, wrong tool use, or miscalibration.</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Single failure mode, no flags.</t>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>
@@ -3059,19 +3128,26 @@
       <c r="AC29" s="12" t="n"/>
       <c r="AD29" s="12" t="n"/>
       <c r="AF29" s="12" t="n"/>
-      <c r="AI29" s="12" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI29" s="12" t="n"/>
       <c r="AJ29" s="12" t="n"/>
       <c r="AK29" s="12" t="n"/>
-      <c r="AL29" s="10" t="inlineStr">
+      <c r="AL29" s="10" t="n"/>
+      <c r="AM29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>The direct customer outcomes of this torque error are a cracked/broken lens (over‑torque) or rattling/vibration noise (under‑torque), which are NVH/appearance issues; there is no explicit accident/injury or regulatory noncompliance stated, and loss/degradation of illumination is not directly attributed to this torque error in the listed effects.</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>Install a DC torque tool programmed to 6 Nm with barcode-linked job selection and OK/NOK lockout so the station cannot proceed if the specified torque is not achieved, preventing wrong tool use and calibration drift from producing under/over‑torque.</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Merged failure mode: 1. Under‑torque (torque not achieved); 2. Over‑torque. Ambiguous - plausible severities: S4 (Lens cracked or broken); S4 (Rattling or vibration noise during driving). Suggested value is the worst case; review before finalizing.</t>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>Merged failure mode: 1. Under‑torque (torque not achieved); 2. Over‑torque. Ambiguous - plausible severities: S4 (Lens cracked or broken); S4 (Rattling or vibration noise during driving). Suggested value is the worst case; review before finalizing. Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
@@ -117,7 +117,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -160,6 +160,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="38">
     <border>
@@ -631,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -1211,8 +1216,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2026,6 +2037,11 @@
       <c r="AJ13" s="196" t="n"/>
       <c r="AK13" s="196" t="n"/>
       <c r="AL13" s="197" t="n"/>
+      <c r="AM13" s="205" t="inlineStr">
+        <is>
+          <t>Suggestion</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22.5" customFormat="1" customHeight="1" s="1">
       <c r="A14" s="198" t="n"/>
@@ -2034,7 +2050,7 @@
       <c r="D14" s="195" t="n"/>
       <c r="E14" s="195" t="n"/>
       <c r="F14" s="199" t="n"/>
-      <c r="G14" s="205" t="n"/>
+      <c r="G14" s="206" t="n"/>
       <c r="H14" s="195" t="n"/>
       <c r="I14" s="195" t="n"/>
       <c r="J14" s="195" t="n"/>
@@ -2075,47 +2091,47 @@
 Name of Process</t>
         </is>
       </c>
-      <c r="B15" s="206" t="n"/>
+      <c r="B15" s="207" t="n"/>
       <c r="C15" s="96" t="inlineStr">
         <is>
           <t>2. Process Step Station No. and Name of
 Focus Element</t>
         </is>
       </c>
-      <c r="D15" s="206" t="n"/>
+      <c r="D15" s="207" t="n"/>
       <c r="E15" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Process Work Element </t>
         </is>
       </c>
-      <c r="F15" s="206" t="n"/>
+      <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
           <t>1. Function of the Process Item Function of System, Subsystem,
 Part Element or Process</t>
         </is>
       </c>
-      <c r="H15" s="206" t="n"/>
+      <c r="H15" s="207" t="n"/>
       <c r="I15" s="96" t="inlineStr">
         <is>
           <t>2. Function of the Process Step and Product Characteristic
 (Quantitative value is optional)</t>
         </is>
       </c>
-      <c r="J15" s="206" t="n"/>
+      <c r="J15" s="207" t="n"/>
       <c r="K15" s="99" t="inlineStr">
         <is>
           <t>3. Function of the Process Work Element and Process
 Characteristic</t>
         </is>
       </c>
-      <c r="L15" s="206" t="n"/>
+      <c r="L15" s="207" t="n"/>
       <c r="M15" s="91" t="inlineStr">
         <is>
           <t>1. Failure Effects (FE) to the Next Higher Level Element and/or End User</t>
         </is>
       </c>
-      <c r="N15" s="206" t="n"/>
+      <c r="N15" s="207" t="n"/>
       <c r="O15" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Severity (S) of FE
@@ -2128,19 +2144,19 @@
 Focus Element</t>
         </is>
       </c>
-      <c r="Q15" s="206" t="n"/>
+      <c r="Q15" s="207" t="n"/>
       <c r="R15" s="99" t="inlineStr">
         <is>
           <t>3. Failure Cause (FC) of the Work Element</t>
         </is>
       </c>
-      <c r="S15" s="206" t="n"/>
+      <c r="S15" s="207" t="n"/>
       <c r="T15" s="141" t="inlineStr">
         <is>
           <t>Current Prevention Control (PC) of FC</t>
         </is>
       </c>
-      <c r="U15" s="206" t="n"/>
+      <c r="U15" s="207" t="n"/>
       <c r="V15" s="109" t="inlineStr">
         <is>
           <t>Occurrence (O) of FC</t>
@@ -2151,7 +2167,7 @@
           <t>Current Detection Controls (DC) of FC or FM</t>
         </is>
       </c>
-      <c r="X15" s="206" t="n"/>
+      <c r="X15" s="207" t="n"/>
       <c r="Y15" s="109" t="inlineStr">
         <is>
           <t>Detection (D) of FC/FM</t>
@@ -2223,116 +2239,116 @@
           <t>Action Prirorty</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AM15" s="208" t="inlineStr">
         <is>
           <t>Severity (S)</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AN15" s="208" t="inlineStr">
         <is>
           <t>Severity Note</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AO15" s="208" t="inlineStr">
         <is>
           <t>Occurrence (O)</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AP15" s="208" t="inlineStr">
         <is>
           <t>Detection (D)</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AQ15" s="208" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AR15" s="208" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22.5" customFormat="1" customHeight="1" s="6">
-      <c r="A16" s="207" t="n"/>
-      <c r="B16" s="208" t="n"/>
-      <c r="C16" s="209" t="n"/>
-      <c r="D16" s="208" t="n"/>
-      <c r="E16" s="209" t="n"/>
-      <c r="F16" s="208" t="n"/>
-      <c r="G16" s="209" t="n"/>
-      <c r="H16" s="208" t="n"/>
-      <c r="I16" s="209" t="n"/>
-      <c r="J16" s="208" t="n"/>
-      <c r="K16" s="209" t="n"/>
-      <c r="L16" s="208" t="n"/>
-      <c r="M16" s="207" t="n"/>
-      <c r="N16" s="208" t="n"/>
-      <c r="O16" s="210" t="n"/>
-      <c r="P16" s="209" t="n"/>
-      <c r="Q16" s="208" t="n"/>
-      <c r="R16" s="209" t="n"/>
-      <c r="S16" s="208" t="n"/>
-      <c r="T16" s="207" t="n"/>
-      <c r="U16" s="208" t="n"/>
-      <c r="V16" s="210" t="n"/>
-      <c r="W16" s="209" t="n"/>
-      <c r="X16" s="208" t="n"/>
-      <c r="Y16" s="210" t="n"/>
-      <c r="Z16" s="210" t="n"/>
-      <c r="AA16" s="211" t="n"/>
-      <c r="AB16" s="212" t="n"/>
-      <c r="AC16" s="210" t="n"/>
-      <c r="AD16" s="210" t="n"/>
-      <c r="AE16" s="210" t="n"/>
-      <c r="AF16" s="210" t="n"/>
-      <c r="AG16" s="210" t="n"/>
-      <c r="AH16" s="210" t="n"/>
-      <c r="AI16" s="210" t="n"/>
-      <c r="AJ16" s="210" t="n"/>
-      <c r="AK16" s="210" t="n"/>
-      <c r="AL16" s="211" t="n"/>
+      <c r="A16" s="209" t="n"/>
+      <c r="B16" s="210" t="n"/>
+      <c r="C16" s="211" t="n"/>
+      <c r="D16" s="210" t="n"/>
+      <c r="E16" s="211" t="n"/>
+      <c r="F16" s="210" t="n"/>
+      <c r="G16" s="211" t="n"/>
+      <c r="H16" s="210" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="210" t="n"/>
+      <c r="K16" s="211" t="n"/>
+      <c r="L16" s="210" t="n"/>
+      <c r="M16" s="209" t="n"/>
+      <c r="N16" s="210" t="n"/>
+      <c r="O16" s="212" t="n"/>
+      <c r="P16" s="211" t="n"/>
+      <c r="Q16" s="210" t="n"/>
+      <c r="R16" s="211" t="n"/>
+      <c r="S16" s="210" t="n"/>
+      <c r="T16" s="209" t="n"/>
+      <c r="U16" s="210" t="n"/>
+      <c r="V16" s="212" t="n"/>
+      <c r="W16" s="211" t="n"/>
+      <c r="X16" s="210" t="n"/>
+      <c r="Y16" s="212" t="n"/>
+      <c r="Z16" s="212" t="n"/>
+      <c r="AA16" s="213" t="n"/>
+      <c r="AB16" s="214" t="n"/>
+      <c r="AC16" s="212" t="n"/>
+      <c r="AD16" s="212" t="n"/>
+      <c r="AE16" s="212" t="n"/>
+      <c r="AF16" s="212" t="n"/>
+      <c r="AG16" s="212" t="n"/>
+      <c r="AH16" s="212" t="n"/>
+      <c r="AI16" s="212" t="n"/>
+      <c r="AJ16" s="212" t="n"/>
+      <c r="AK16" s="212" t="n"/>
+      <c r="AL16" s="213" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
       <c r="B17" s="199" t="n"/>
-      <c r="C17" s="205" t="n"/>
+      <c r="C17" s="206" t="n"/>
       <c r="D17" s="199" t="n"/>
-      <c r="E17" s="205" t="n"/>
+      <c r="E17" s="206" t="n"/>
       <c r="F17" s="199" t="n"/>
-      <c r="G17" s="205" t="n"/>
+      <c r="G17" s="206" t="n"/>
       <c r="H17" s="199" t="n"/>
-      <c r="I17" s="205" t="n"/>
+      <c r="I17" s="206" t="n"/>
       <c r="J17" s="199" t="n"/>
-      <c r="K17" s="205" t="n"/>
+      <c r="K17" s="206" t="n"/>
       <c r="L17" s="199" t="n"/>
       <c r="M17" s="198" t="n"/>
       <c r="N17" s="199" t="n"/>
-      <c r="O17" s="213" t="n"/>
-      <c r="P17" s="205" t="n"/>
+      <c r="O17" s="215" t="n"/>
+      <c r="P17" s="206" t="n"/>
       <c r="Q17" s="199" t="n"/>
-      <c r="R17" s="205" t="n"/>
+      <c r="R17" s="206" t="n"/>
       <c r="S17" s="199" t="n"/>
       <c r="T17" s="198" t="n"/>
       <c r="U17" s="199" t="n"/>
-      <c r="V17" s="213" t="n"/>
-      <c r="W17" s="205" t="n"/>
+      <c r="V17" s="215" t="n"/>
+      <c r="W17" s="206" t="n"/>
       <c r="X17" s="199" t="n"/>
-      <c r="Y17" s="213" t="n"/>
-      <c r="Z17" s="213" t="n"/>
-      <c r="AA17" s="214" t="n"/>
-      <c r="AB17" s="215" t="n"/>
-      <c r="AC17" s="213" t="n"/>
-      <c r="AD17" s="213" t="n"/>
-      <c r="AE17" s="213" t="n"/>
-      <c r="AF17" s="213" t="n"/>
-      <c r="AG17" s="213" t="n"/>
-      <c r="AH17" s="213" t="n"/>
-      <c r="AI17" s="213" t="n"/>
-      <c r="AJ17" s="213" t="n"/>
-      <c r="AK17" s="213" t="n"/>
-      <c r="AL17" s="214" t="n"/>
+      <c r="Y17" s="215" t="n"/>
+      <c r="Z17" s="215" t="n"/>
+      <c r="AA17" s="216" t="n"/>
+      <c r="AB17" s="217" t="n"/>
+      <c r="AC17" s="215" t="n"/>
+      <c r="AD17" s="215" t="n"/>
+      <c r="AE17" s="215" t="n"/>
+      <c r="AF17" s="215" t="n"/>
+      <c r="AG17" s="215" t="n"/>
+      <c r="AH17" s="215" t="n"/>
+      <c r="AI17" s="215" t="n"/>
+      <c r="AJ17" s="215" t="n"/>
+      <c r="AK17" s="215" t="n"/>
+      <c r="AL17" s="216" t="n"/>
     </row>
     <row r="18" ht="102" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -2340,8 +2356,8 @@
           <t>HEAD LAMP STAGE</t>
         </is>
       </c>
-      <c r="B18" s="206" t="n"/>
-      <c r="C18" s="216" t="inlineStr">
+      <c r="B18" s="207" t="n"/>
+      <c r="C18" s="218" t="inlineStr">
         <is>
           <t xml:space="preserve">Operation No: 
 Stage: 
@@ -2349,8 +2365,8 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="206" t="n"/>
-      <c r="E18" s="217" t="inlineStr">
+      <c r="D18" s="207" t="n"/>
+      <c r="E18" s="219" t="inlineStr">
         <is>
           <t>1 Man - Operator
 2.Machine-  
@@ -2363,8 +2379,8 @@
 6.Measurement- NA</t>
         </is>
       </c>
-      <c r="F18" s="206" t="n"/>
-      <c r="G18" s="218" t="inlineStr">
+      <c r="F18" s="207" t="n"/>
+      <c r="G18" s="220" t="inlineStr">
         <is>
           <t>Your Plant :
 Headlamp assembly in specific design (bulb/LED assembly, lens fitting, aiming, electrical connection)
@@ -2375,14 +2391,14 @@
 3. Meet legal/regulatory lighting requirements (beam pattern, intensity, color)</t>
         </is>
       </c>
-      <c r="H18" s="206" t="n"/>
+      <c r="H18" s="207" t="n"/>
       <c r="I18" s="162" t="inlineStr">
         <is>
           <t>COLLECTION OF HEAD LAMP</t>
         </is>
       </c>
-      <c r="J18" s="206" t="n"/>
-      <c r="K18" s="219" t="inlineStr">
+      <c r="J18" s="207" t="n"/>
+      <c r="K18" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Man: 
 1. COLLECT THE HEAD LAMP LH / RH SIDE FROM STORAGE AREA AND SCAN THE PART
@@ -2398,7 +2414,7 @@
 </t>
         </is>
       </c>
-      <c r="L18" s="206" t="n"/>
+      <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -2412,7 +2428,7 @@
 3. Customer dissatisfaction</t>
         </is>
       </c>
-      <c r="N18" s="206" t="n"/>
+      <c r="N18" s="207" t="n"/>
       <c r="O18" s="162" t="n">
         <v>5</v>
       </c>
@@ -2421,7 +2437,7 @@
           <t>SCRATCH / DAMAGE ON HEAD LAMP</t>
         </is>
       </c>
-      <c r="Q18" s="206" t="n"/>
+      <c r="Q18" s="207" t="n"/>
       <c r="R18" s="155" t="n"/>
       <c r="S18" s="201" t="n"/>
       <c r="T18" s="156" t="n"/>
@@ -2429,14 +2445,14 @@
       <c r="V18" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="220" t="inlineStr">
+      <c r="W18" s="222" t="inlineStr">
         <is>
           <t>1. SELF CHECK, 
 2. CHECKMAN CHECKING,
 3. ECOS SYSTEM</t>
         </is>
       </c>
-      <c r="X18" s="206" t="n"/>
+      <c r="X18" s="207" t="n"/>
       <c r="Y18" s="162" t="n">
         <v>5</v>
       </c>
@@ -2476,21 +2492,21 @@
       </c>
     </row>
     <row r="19" ht="207" customFormat="1" customHeight="1" s="8">
-      <c r="B19" s="208" t="n"/>
-      <c r="C19" s="209" t="n"/>
-      <c r="D19" s="208" t="n"/>
-      <c r="E19" s="209" t="n"/>
-      <c r="F19" s="208" t="n"/>
-      <c r="G19" s="209" t="n"/>
-      <c r="H19" s="208" t="n"/>
-      <c r="I19" s="209" t="n"/>
-      <c r="J19" s="208" t="n"/>
-      <c r="K19" s="209" t="n"/>
-      <c r="L19" s="208" t="n"/>
-      <c r="M19" s="209" t="n"/>
-      <c r="N19" s="208" t="n"/>
-      <c r="O19" s="210" t="n"/>
-      <c r="P19" s="205" t="n"/>
+      <c r="B19" s="210" t="n"/>
+      <c r="C19" s="211" t="n"/>
+      <c r="D19" s="210" t="n"/>
+      <c r="E19" s="211" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="211" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="211" t="n"/>
+      <c r="J19" s="210" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="210" t="n"/>
+      <c r="M19" s="211" t="n"/>
+      <c r="N19" s="210" t="n"/>
+      <c r="O19" s="212" t="n"/>
+      <c r="P19" s="206" t="n"/>
       <c r="Q19" s="199" t="n"/>
       <c r="R19" s="43" t="inlineStr">
         <is>
@@ -2498,18 +2514,18 @@
 PARTS MIX-UP IN STORAGE TROLLEY.</t>
         </is>
       </c>
-      <c r="S19" s="206" t="n"/>
+      <c r="S19" s="207" t="n"/>
       <c r="T19" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, PART TRACEABILITY, Sequencing part</t>
         </is>
       </c>
-      <c r="U19" s="206" t="n"/>
-      <c r="V19" s="210" t="n"/>
-      <c r="W19" s="209" t="n"/>
-      <c r="X19" s="208" t="n"/>
-      <c r="Y19" s="210" t="n"/>
-      <c r="Z19" s="210" t="n"/>
+      <c r="U19" s="207" t="n"/>
+      <c r="V19" s="212" t="n"/>
+      <c r="W19" s="211" t="n"/>
+      <c r="X19" s="210" t="n"/>
+      <c r="Y19" s="212" t="n"/>
+      <c r="Z19" s="212" t="n"/>
       <c r="AA19" s="162" t="n"/>
       <c r="AB19" s="162" t="n"/>
       <c r="AC19" s="45" t="n"/>
@@ -2521,20 +2537,20 @@
       <c r="AL19" s="35" t="n"/>
     </row>
     <row r="20" ht="117" customFormat="1" customHeight="1" s="8">
-      <c r="B20" s="208" t="n"/>
-      <c r="C20" s="209" t="n"/>
-      <c r="D20" s="208" t="n"/>
-      <c r="E20" s="209" t="n"/>
-      <c r="F20" s="208" t="n"/>
-      <c r="G20" s="209" t="n"/>
-      <c r="H20" s="208" t="n"/>
-      <c r="I20" s="209" t="n"/>
-      <c r="J20" s="208" t="n"/>
-      <c r="K20" s="209" t="n"/>
-      <c r="L20" s="208" t="n"/>
-      <c r="M20" s="209" t="n"/>
-      <c r="N20" s="208" t="n"/>
-      <c r="O20" s="210" t="n"/>
+      <c r="B20" s="210" t="n"/>
+      <c r="C20" s="211" t="n"/>
+      <c r="D20" s="210" t="n"/>
+      <c r="E20" s="211" t="n"/>
+      <c r="F20" s="210" t="n"/>
+      <c r="G20" s="211" t="n"/>
+      <c r="H20" s="210" t="n"/>
+      <c r="I20" s="211" t="n"/>
+      <c r="J20" s="210" t="n"/>
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="210" t="n"/>
+      <c r="M20" s="211" t="n"/>
+      <c r="N20" s="210" t="n"/>
+      <c r="O20" s="212" t="n"/>
       <c r="P20" s="162" t="inlineStr">
         <is>
           <t xml:space="preserve">FITMENT IS NOT FIRM
@@ -2542,16 +2558,16 @@
 ( NOT AS PER MODEL) </t>
         </is>
       </c>
-      <c r="Q20" s="206" t="n"/>
+      <c r="Q20" s="207" t="n"/>
       <c r="R20" s="155" t="n"/>
       <c r="S20" s="201" t="n"/>
       <c r="T20" s="156" t="n"/>
       <c r="U20" s="201" t="n"/>
-      <c r="V20" s="210" t="n"/>
-      <c r="W20" s="209" t="n"/>
-      <c r="X20" s="208" t="n"/>
-      <c r="Y20" s="210" t="n"/>
-      <c r="Z20" s="210" t="n"/>
+      <c r="V20" s="212" t="n"/>
+      <c r="W20" s="211" t="n"/>
+      <c r="X20" s="210" t="n"/>
+      <c r="Y20" s="212" t="n"/>
+      <c r="Z20" s="212" t="n"/>
       <c r="AA20" s="162" t="n"/>
       <c r="AB20" s="162" t="n"/>
       <c r="AC20" s="45" t="n"/>
@@ -2581,21 +2597,21 @@
       </c>
     </row>
     <row r="21" ht="153" customFormat="1" customHeight="1" s="8">
-      <c r="B21" s="208" t="n"/>
-      <c r="C21" s="209" t="n"/>
-      <c r="D21" s="208" t="n"/>
-      <c r="E21" s="209" t="n"/>
-      <c r="F21" s="208" t="n"/>
-      <c r="G21" s="209" t="n"/>
-      <c r="H21" s="208" t="n"/>
-      <c r="I21" s="205" t="n"/>
+      <c r="B21" s="210" t="n"/>
+      <c r="C21" s="211" t="n"/>
+      <c r="D21" s="210" t="n"/>
+      <c r="E21" s="211" t="n"/>
+      <c r="F21" s="210" t="n"/>
+      <c r="G21" s="211" t="n"/>
+      <c r="H21" s="210" t="n"/>
+      <c r="I21" s="206" t="n"/>
       <c r="J21" s="199" t="n"/>
-      <c r="K21" s="209" t="n"/>
-      <c r="L21" s="208" t="n"/>
-      <c r="M21" s="205" t="n"/>
+      <c r="K21" s="211" t="n"/>
+      <c r="L21" s="210" t="n"/>
+      <c r="M21" s="206" t="n"/>
       <c r="N21" s="199" t="n"/>
-      <c r="O21" s="213" t="n"/>
-      <c r="P21" s="205" t="n"/>
+      <c r="O21" s="215" t="n"/>
+      <c r="P21" s="206" t="n"/>
       <c r="Q21" s="199" t="n"/>
       <c r="R21" s="43" t="inlineStr">
         <is>
@@ -2603,18 +2619,18 @@
 PARTS MIX-UP IN STORAGE TROLLEY.</t>
         </is>
       </c>
-      <c r="S21" s="206" t="n"/>
+      <c r="S21" s="207" t="n"/>
       <c r="T21" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, PART TRACEABILITY, Sequencing part</t>
         </is>
       </c>
-      <c r="U21" s="206" t="n"/>
-      <c r="V21" s="213" t="n"/>
-      <c r="W21" s="205" t="n"/>
+      <c r="U21" s="207" t="n"/>
+      <c r="V21" s="215" t="n"/>
+      <c r="W21" s="206" t="n"/>
       <c r="X21" s="199" t="n"/>
-      <c r="Y21" s="213" t="n"/>
-      <c r="Z21" s="213" t="n"/>
+      <c r="Y21" s="215" t="n"/>
+      <c r="Z21" s="215" t="n"/>
       <c r="AA21" s="162" t="n"/>
       <c r="AB21" s="162" t="n"/>
       <c r="AC21" s="45" t="n"/>
@@ -2626,22 +2642,22 @@
       <c r="AL21" s="35" t="n"/>
     </row>
     <row r="22" ht="119.25" customFormat="1" customHeight="1" s="8">
-      <c r="B22" s="208" t="n"/>
-      <c r="C22" s="209" t="n"/>
-      <c r="D22" s="208" t="n"/>
-      <c r="E22" s="209" t="n"/>
-      <c r="F22" s="208" t="n"/>
-      <c r="G22" s="209" t="n"/>
-      <c r="H22" s="208" t="n"/>
+      <c r="B22" s="210" t="n"/>
+      <c r="C22" s="211" t="n"/>
+      <c r="D22" s="210" t="n"/>
+      <c r="E22" s="211" t="n"/>
+      <c r="F22" s="210" t="n"/>
+      <c r="G22" s="211" t="n"/>
+      <c r="H22" s="210" t="n"/>
       <c r="I22" s="154" t="inlineStr">
         <is>
           <t>ENSURE LOCKING OF CONNECTORS</t>
         </is>
       </c>
-      <c r="J22" s="206" t="n"/>
-      <c r="K22" s="209" t="n"/>
-      <c r="L22" s="208" t="n"/>
-      <c r="M22" s="221" t="inlineStr">
+      <c r="J22" s="207" t="n"/>
+      <c r="K22" s="211" t="n"/>
+      <c r="L22" s="210" t="n"/>
+      <c r="M22" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. Wiring harness partially connected (loose fitment)
@@ -2655,7 +2671,7 @@
 4. Increased risk of accident</t>
         </is>
       </c>
-      <c r="N22" s="206" t="n"/>
+      <c r="N22" s="207" t="n"/>
       <c r="O22" s="146" t="n"/>
       <c r="P22" s="162" t="inlineStr">
         <is>
@@ -2663,7 +2679,7 @@
 POOR LOCKING</t>
         </is>
       </c>
-      <c r="Q22" s="206" t="n"/>
+      <c r="Q22" s="207" t="n"/>
       <c r="R22" s="155" t="n"/>
       <c r="S22" s="201" t="n"/>
       <c r="T22" s="156" t="n"/>
@@ -2702,23 +2718,23 @@
       </c>
     </row>
     <row r="23" ht="186.95" customFormat="1" customHeight="1" s="14">
-      <c r="B23" s="208" t="n"/>
-      <c r="C23" s="209" t="n"/>
-      <c r="D23" s="208" t="n"/>
-      <c r="E23" s="209" t="n"/>
-      <c r="F23" s="208" t="n"/>
-      <c r="G23" s="209" t="n"/>
-      <c r="H23" s="208" t="n"/>
-      <c r="I23" s="205" t="n"/>
+      <c r="B23" s="210" t="n"/>
+      <c r="C23" s="211" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="211" t="n"/>
+      <c r="F23" s="210" t="n"/>
+      <c r="G23" s="211" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="206" t="n"/>
       <c r="J23" s="199" t="n"/>
-      <c r="K23" s="209" t="n"/>
-      <c r="L23" s="208" t="n"/>
-      <c r="M23" s="209" t="n"/>
-      <c r="N23" s="208" t="n"/>
+      <c r="K23" s="211" t="n"/>
+      <c r="L23" s="210" t="n"/>
+      <c r="M23" s="211" t="n"/>
+      <c r="N23" s="210" t="n"/>
       <c r="O23" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="P23" s="205" t="n"/>
+      <c r="P23" s="206" t="n"/>
       <c r="Q23" s="199" t="n"/>
       <c r="R23" s="155" t="inlineStr">
         <is>
@@ -2733,7 +2749,7 @@
           <t>PROPER CONNECTION IS ENSURED ON STAGE AND MARKING ON CONNECTION</t>
         </is>
       </c>
-      <c r="U23" s="206" t="n"/>
+      <c r="U23" s="207" t="n"/>
       <c r="V23" s="162" t="n">
         <v>3</v>
       </c>
@@ -2744,7 +2760,7 @@
 ECOS SYSTEM</t>
         </is>
       </c>
-      <c r="X23" s="206" t="n"/>
+      <c r="X23" s="207" t="n"/>
       <c r="Y23" s="45" t="n">
         <v>5</v>
       </c>
@@ -2767,40 +2783,40 @@
       <c r="AL23" s="10" t="n"/>
     </row>
     <row r="24" ht="130.5" customFormat="1" customHeight="1" s="14">
-      <c r="B24" s="208" t="n"/>
-      <c r="C24" s="209" t="n"/>
-      <c r="D24" s="208" t="n"/>
-      <c r="E24" s="209" t="n"/>
-      <c r="F24" s="208" t="n"/>
-      <c r="G24" s="209" t="n"/>
-      <c r="H24" s="208" t="n"/>
+      <c r="B24" s="210" t="n"/>
+      <c r="C24" s="211" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="211" t="n"/>
+      <c r="F24" s="210" t="n"/>
+      <c r="G24" s="211" t="n"/>
+      <c r="H24" s="210" t="n"/>
       <c r="I24" s="154" t="inlineStr">
         <is>
           <t>PREFITMENT OF ALL
  H / L BOLTS</t>
         </is>
       </c>
-      <c r="J24" s="206" t="n"/>
-      <c r="K24" s="209" t="n"/>
-      <c r="L24" s="208" t="n"/>
-      <c r="M24" s="209" t="n"/>
-      <c r="N24" s="208" t="n"/>
-      <c r="O24" s="210" t="n"/>
+      <c r="J24" s="207" t="n"/>
+      <c r="K24" s="211" t="n"/>
+      <c r="L24" s="210" t="n"/>
+      <c r="M24" s="211" t="n"/>
+      <c r="N24" s="210" t="n"/>
+      <c r="O24" s="212" t="n"/>
       <c r="P24" s="162" t="inlineStr">
         <is>
           <t>OPERATOR FAILED TO PREFIT BOLTS</t>
         </is>
       </c>
-      <c r="Q24" s="206" t="n"/>
+      <c r="Q24" s="207" t="n"/>
       <c r="R24" s="155" t="n"/>
       <c r="S24" s="201" t="n"/>
       <c r="T24" s="156" t="n"/>
       <c r="U24" s="201" t="n"/>
-      <c r="V24" s="210" t="n"/>
-      <c r="W24" s="209" t="n"/>
-      <c r="X24" s="208" t="n"/>
-      <c r="Y24" s="210" t="n"/>
-      <c r="Z24" s="210" t="n"/>
+      <c r="V24" s="212" t="n"/>
+      <c r="W24" s="211" t="n"/>
+      <c r="X24" s="210" t="n"/>
+      <c r="Y24" s="212" t="n"/>
+      <c r="Z24" s="212" t="n"/>
       <c r="AA24" s="17" t="n"/>
       <c r="AB24" s="16" t="n"/>
       <c r="AC24" s="12" t="n"/>
@@ -2833,21 +2849,21 @@
       </c>
     </row>
     <row r="25" ht="130.5" customFormat="1" customHeight="1" s="14">
-      <c r="B25" s="208" t="n"/>
-      <c r="C25" s="209" t="n"/>
-      <c r="D25" s="208" t="n"/>
-      <c r="E25" s="209" t="n"/>
-      <c r="F25" s="208" t="n"/>
-      <c r="G25" s="209" t="n"/>
-      <c r="H25" s="208" t="n"/>
-      <c r="I25" s="205" t="n"/>
+      <c r="B25" s="210" t="n"/>
+      <c r="C25" s="211" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="211" t="n"/>
+      <c r="F25" s="210" t="n"/>
+      <c r="G25" s="211" t="n"/>
+      <c r="H25" s="210" t="n"/>
+      <c r="I25" s="206" t="n"/>
       <c r="J25" s="199" t="n"/>
-      <c r="K25" s="209" t="n"/>
-      <c r="L25" s="208" t="n"/>
-      <c r="M25" s="205" t="n"/>
+      <c r="K25" s="211" t="n"/>
+      <c r="L25" s="210" t="n"/>
+      <c r="M25" s="206" t="n"/>
       <c r="N25" s="199" t="n"/>
-      <c r="O25" s="210" t="n"/>
-      <c r="P25" s="205" t="n"/>
+      <c r="O25" s="212" t="n"/>
+      <c r="P25" s="206" t="n"/>
       <c r="Q25" s="199" t="n"/>
       <c r="R25" s="155" t="inlineStr">
         <is>
@@ -2863,11 +2879,11 @@
         </is>
       </c>
       <c r="U25" s="201" t="n"/>
-      <c r="V25" s="213" t="n"/>
-      <c r="W25" s="209" t="n"/>
-      <c r="X25" s="208" t="n"/>
-      <c r="Y25" s="210" t="n"/>
-      <c r="Z25" s="213" t="n"/>
+      <c r="V25" s="215" t="n"/>
+      <c r="W25" s="211" t="n"/>
+      <c r="X25" s="210" t="n"/>
+      <c r="Y25" s="212" t="n"/>
+      <c r="Z25" s="215" t="n"/>
       <c r="AA25" s="15" t="n"/>
       <c r="AB25" s="16" t="n"/>
       <c r="AC25" s="12" t="n"/>
@@ -2882,22 +2898,22 @@
       <c r="AL25" s="10" t="n"/>
     </row>
     <row r="26" ht="135" customFormat="1" customHeight="1" s="14">
-      <c r="B26" s="208" t="n"/>
-      <c r="C26" s="209" t="n"/>
-      <c r="D26" s="208" t="n"/>
-      <c r="E26" s="209" t="n"/>
-      <c r="F26" s="208" t="n"/>
-      <c r="G26" s="209" t="n"/>
-      <c r="H26" s="208" t="n"/>
+      <c r="B26" s="210" t="n"/>
+      <c r="C26" s="211" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="210" t="n"/>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="210" t="n"/>
       <c r="I26" s="162" t="inlineStr">
         <is>
           <t>FLUSHNESS &amp; GAPS MAINTAINED BETWEEN HEAD LAMP &amp; FENDER EDGE</t>
         </is>
       </c>
-      <c r="J26" s="206" t="n"/>
-      <c r="K26" s="209" t="n"/>
-      <c r="L26" s="208" t="n"/>
-      <c r="M26" s="221" t="inlineStr">
+      <c r="J26" s="207" t="n"/>
+      <c r="K26" s="211" t="n"/>
+      <c r="L26" s="210" t="n"/>
+      <c r="M26" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
@@ -2911,21 +2927,21 @@
 5. Driver discomfort or eye strain</t>
         </is>
       </c>
-      <c r="N26" s="206" t="n"/>
+      <c r="N26" s="207" t="n"/>
       <c r="O26" s="146" t="n"/>
       <c r="P26" s="162" t="inlineStr">
         <is>
           <t>OPERATOR FAILED TO FIT SCREWS AND NOT MAINTAINED GAP</t>
         </is>
       </c>
-      <c r="Q26" s="206" t="n"/>
+      <c r="Q26" s="207" t="n"/>
       <c r="R26" s="155" t="n"/>
       <c r="S26" s="201" t="n"/>
       <c r="T26" s="156" t="n"/>
       <c r="U26" s="201" t="n"/>
       <c r="V26" s="45" t="n"/>
-      <c r="W26" s="209" t="n"/>
-      <c r="X26" s="208" t="n"/>
+      <c r="W26" s="211" t="n"/>
+      <c r="X26" s="210" t="n"/>
       <c r="Y26" s="146" t="n"/>
       <c r="Z26" s="186" t="n"/>
       <c r="AA26" s="15" t="n"/>
@@ -2960,23 +2976,23 @@
       </c>
     </row>
     <row r="27" ht="156" customFormat="1" customHeight="1" s="13">
-      <c r="B27" s="208" t="n"/>
-      <c r="C27" s="209" t="n"/>
-      <c r="D27" s="208" t="n"/>
-      <c r="E27" s="209" t="n"/>
-      <c r="F27" s="208" t="n"/>
-      <c r="G27" s="209" t="n"/>
-      <c r="H27" s="208" t="n"/>
-      <c r="I27" s="205" t="n"/>
+      <c r="B27" s="210" t="n"/>
+      <c r="C27" s="211" t="n"/>
+      <c r="D27" s="210" t="n"/>
+      <c r="E27" s="211" t="n"/>
+      <c r="F27" s="210" t="n"/>
+      <c r="G27" s="211" t="n"/>
+      <c r="H27" s="210" t="n"/>
+      <c r="I27" s="206" t="n"/>
       <c r="J27" s="199" t="n"/>
-      <c r="K27" s="209" t="n"/>
-      <c r="L27" s="208" t="n"/>
-      <c r="M27" s="209" t="n"/>
-      <c r="N27" s="208" t="n"/>
+      <c r="K27" s="211" t="n"/>
+      <c r="L27" s="210" t="n"/>
+      <c r="M27" s="211" t="n"/>
+      <c r="N27" s="210" t="n"/>
       <c r="O27" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="P27" s="205" t="n"/>
+      <c r="P27" s="206" t="n"/>
       <c r="Q27" s="199" t="n"/>
       <c r="R27" s="155" t="inlineStr">
         <is>
@@ -2994,7 +3010,7 @@
       <c r="V27" s="162" t="n">
         <v>3</v>
       </c>
-      <c r="W27" s="205" t="n"/>
+      <c r="W27" s="206" t="n"/>
       <c r="X27" s="199" t="n"/>
       <c r="Y27" s="162" t="n">
         <v>5</v>
@@ -3015,24 +3031,24 @@
       <c r="AL27" s="10" t="n"/>
     </row>
     <row r="28" ht="151.5" customFormat="1" customHeight="1" s="13">
-      <c r="B28" s="208" t="n"/>
-      <c r="C28" s="209" t="n"/>
-      <c r="D28" s="208" t="n"/>
-      <c r="E28" s="209" t="n"/>
-      <c r="F28" s="208" t="n"/>
-      <c r="G28" s="209" t="n"/>
-      <c r="H28" s="208" t="n"/>
-      <c r="I28" s="222" t="inlineStr">
+      <c r="B28" s="210" t="n"/>
+      <c r="C28" s="211" t="n"/>
+      <c r="D28" s="210" t="n"/>
+      <c r="E28" s="211" t="n"/>
+      <c r="F28" s="210" t="n"/>
+      <c r="G28" s="211" t="n"/>
+      <c r="H28" s="210" t="n"/>
+      <c r="I28" s="224" t="inlineStr">
         <is>
           <t>PROPER TIGHTENING OF JOINT</t>
         </is>
       </c>
-      <c r="J28" s="208" t="n"/>
-      <c r="K28" s="209" t="n"/>
-      <c r="L28" s="208" t="n"/>
-      <c r="M28" s="209" t="n"/>
-      <c r="N28" s="208" t="n"/>
-      <c r="O28" s="210" t="n"/>
+      <c r="J28" s="210" t="n"/>
+      <c r="K28" s="211" t="n"/>
+      <c r="L28" s="210" t="n"/>
+      <c r="M28" s="211" t="n"/>
+      <c r="N28" s="210" t="n"/>
+      <c r="O28" s="212" t="n"/>
       <c r="P28" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED-UNDER TORQUE</t>
@@ -3046,25 +3062,25 @@
 3.  IMPROPER POWER TOOL CALIBRATION</t>
         </is>
       </c>
-      <c r="S28" s="206" t="n"/>
+      <c r="S28" s="207" t="n"/>
       <c r="T28" s="175" t="inlineStr">
         <is>
           <t xml:space="preserve">
 PROVISION OF DEDICATED  POWER TOOL FOR THIS APPLICATION, VISUAL / IDENTIFICATION ON POWER TOOL</t>
         </is>
       </c>
-      <c r="U28" s="206" t="n"/>
-      <c r="V28" s="210" t="n"/>
-      <c r="W28" s="220" t="inlineStr">
+      <c r="U28" s="207" t="n"/>
+      <c r="V28" s="212" t="n"/>
+      <c r="W28" s="222" t="inlineStr">
         <is>
           <t>1. SELF CHECK WITH MARKING,
 2. CHECKMAN CHECKING,
 3. CALIBRATION RECORD</t>
         </is>
       </c>
-      <c r="X28" s="206" t="n"/>
-      <c r="Y28" s="210" t="n"/>
-      <c r="Z28" s="210" t="n"/>
+      <c r="X28" s="207" t="n"/>
+      <c r="Y28" s="212" t="n"/>
+      <c r="Z28" s="212" t="n"/>
       <c r="AA28" s="17" t="n"/>
       <c r="AB28" s="9" t="n"/>
       <c r="AC28" s="12" t="n"/>
@@ -3094,35 +3110,35 @@
       </c>
     </row>
     <row r="29" ht="118.5" customFormat="1" customHeight="1" s="13">
-      <c r="B29" s="208" t="n"/>
-      <c r="C29" s="209" t="n"/>
-      <c r="D29" s="208" t="n"/>
-      <c r="E29" s="209" t="n"/>
-      <c r="F29" s="208" t="n"/>
-      <c r="G29" s="209" t="n"/>
-      <c r="H29" s="208" t="n"/>
-      <c r="I29" s="205" t="n"/>
+      <c r="B29" s="210" t="n"/>
+      <c r="C29" s="211" t="n"/>
+      <c r="D29" s="210" t="n"/>
+      <c r="E29" s="211" t="n"/>
+      <c r="F29" s="210" t="n"/>
+      <c r="G29" s="211" t="n"/>
+      <c r="H29" s="210" t="n"/>
+      <c r="I29" s="206" t="n"/>
       <c r="J29" s="199" t="n"/>
-      <c r="K29" s="209" t="n"/>
-      <c r="L29" s="208" t="n"/>
-      <c r="M29" s="205" t="n"/>
+      <c r="K29" s="211" t="n"/>
+      <c r="L29" s="210" t="n"/>
+      <c r="M29" s="206" t="n"/>
       <c r="N29" s="199" t="n"/>
-      <c r="O29" s="213" t="n"/>
+      <c r="O29" s="215" t="n"/>
       <c r="P29" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED - OVER TORQUE</t>
         </is>
       </c>
       <c r="Q29" s="201" t="n"/>
-      <c r="R29" s="205" t="n"/>
+      <c r="R29" s="206" t="n"/>
       <c r="S29" s="199" t="n"/>
-      <c r="T29" s="205" t="n"/>
+      <c r="T29" s="206" t="n"/>
       <c r="U29" s="199" t="n"/>
-      <c r="V29" s="213" t="n"/>
-      <c r="W29" s="205" t="n"/>
+      <c r="V29" s="215" t="n"/>
+      <c r="W29" s="206" t="n"/>
       <c r="X29" s="199" t="n"/>
-      <c r="Y29" s="213" t="n"/>
-      <c r="Z29" s="213" t="n"/>
+      <c r="Y29" s="215" t="n"/>
+      <c r="Z29" s="215" t="n"/>
       <c r="AA29" s="17" t="n"/>
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="12" t="n"/>
@@ -3153,10 +3169,11 @@
     </row>
     <row r="30" customFormat="1" s="18"/>
   </sheetData>
-  <mergeCells count="125">
+  <mergeCells count="132">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="K18:L29"/>
     <mergeCell ref="I24:J25"/>
+    <mergeCell ref="AM15:AM17"/>
     <mergeCell ref="AE15:AE17"/>
     <mergeCell ref="AG15:AG17"/>
     <mergeCell ref="C15:D17"/>
@@ -3172,6 +3189,7 @@
     <mergeCell ref="K9:T9"/>
     <mergeCell ref="K5:T5"/>
     <mergeCell ref="T28:U29"/>
+    <mergeCell ref="AN15:AN17"/>
     <mergeCell ref="K11:T11"/>
     <mergeCell ref="I3:T4"/>
     <mergeCell ref="A6:C6"/>
@@ -3180,7 +3198,9 @@
     <mergeCell ref="Y18:Y21"/>
     <mergeCell ref="R18:S18"/>
     <mergeCell ref="T27:U27"/>
+    <mergeCell ref="AP15:AP17"/>
     <mergeCell ref="K8:T8"/>
+    <mergeCell ref="AR15:AR17"/>
     <mergeCell ref="Z23:Z25"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="M22:N25"/>
@@ -3195,6 +3215,7 @@
     <mergeCell ref="Z18:Z21"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P18:Q19"/>
+    <mergeCell ref="AQ15:AQ17"/>
     <mergeCell ref="Y23:Y25"/>
     <mergeCell ref="Z27:Z29"/>
     <mergeCell ref="D5:F5"/>
@@ -3239,6 +3260,7 @@
     <mergeCell ref="P22:Q23"/>
     <mergeCell ref="V18:V21"/>
     <mergeCell ref="T19:U19"/>
+    <mergeCell ref="AO15:AO17"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="V27:V29"/>
     <mergeCell ref="A3:H4"/>
@@ -3261,6 +3283,7 @@
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="M13:S14"/>
     <mergeCell ref="P24:Q25"/>
+    <mergeCell ref="AM13:AR14"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="Z15:Z17"/>
     <mergeCell ref="AB15:AB17"/>
@@ -3735,7 +3758,7 @@
       <c r="D14" s="195" t="n"/>
       <c r="E14" s="195" t="n"/>
       <c r="F14" s="199" t="n"/>
-      <c r="G14" s="205" t="n"/>
+      <c r="G14" s="206" t="n"/>
       <c r="H14" s="195" t="n"/>
       <c r="I14" s="195" t="n"/>
       <c r="J14" s="195" t="n"/>
@@ -3776,47 +3799,47 @@
 Name of Process</t>
         </is>
       </c>
-      <c r="B15" s="206" t="n"/>
+      <c r="B15" s="207" t="n"/>
       <c r="C15" s="96" t="inlineStr">
         <is>
           <t>2. Process Step Station No. and Name of
 Focus Element</t>
         </is>
       </c>
-      <c r="D15" s="206" t="n"/>
+      <c r="D15" s="207" t="n"/>
       <c r="E15" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Process Work Element </t>
         </is>
       </c>
-      <c r="F15" s="206" t="n"/>
+      <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
           <t>1. Function of the Process Item Function of System, Subsystem,
 Part Element or Process</t>
         </is>
       </c>
-      <c r="H15" s="206" t="n"/>
+      <c r="H15" s="207" t="n"/>
       <c r="I15" s="96" t="inlineStr">
         <is>
           <t>2. Function of the Process Step and Product Characteristic
 (Quantitative value is optional)</t>
         </is>
       </c>
-      <c r="J15" s="206" t="n"/>
+      <c r="J15" s="207" t="n"/>
       <c r="K15" s="99" t="inlineStr">
         <is>
           <t>3. Function of the Process Work Element and Process
 Characteristic</t>
         </is>
       </c>
-      <c r="L15" s="206" t="n"/>
+      <c r="L15" s="207" t="n"/>
       <c r="M15" s="91" t="inlineStr">
         <is>
           <t>1. Failure Effects (FE) to the Next Higher Level Element and/or End User</t>
         </is>
       </c>
-      <c r="N15" s="206" t="n"/>
+      <c r="N15" s="207" t="n"/>
       <c r="O15" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Severity (S) of FE
@@ -3829,19 +3852,19 @@
 Focus Element</t>
         </is>
       </c>
-      <c r="Q15" s="206" t="n"/>
+      <c r="Q15" s="207" t="n"/>
       <c r="R15" s="99" t="inlineStr">
         <is>
           <t>3. Failure Cause (FC) of the Work Element</t>
         </is>
       </c>
-      <c r="S15" s="206" t="n"/>
+      <c r="S15" s="207" t="n"/>
       <c r="T15" s="141" t="inlineStr">
         <is>
           <t>Current Prevention Control (PC) of FC</t>
         </is>
       </c>
-      <c r="U15" s="206" t="n"/>
+      <c r="U15" s="207" t="n"/>
       <c r="V15" s="109" t="inlineStr">
         <is>
           <t>Occurrence (O) of FC</t>
@@ -3852,7 +3875,7 @@
           <t>Current Detection Controls (DC) of FC or FM</t>
         </is>
       </c>
-      <c r="X15" s="206" t="n"/>
+      <c r="X15" s="207" t="n"/>
       <c r="Y15" s="109" t="inlineStr">
         <is>
           <t>Detection (D) of FC/FM</t>
@@ -3926,84 +3949,84 @@
       </c>
     </row>
     <row r="16" ht="22.5" customFormat="1" customHeight="1" s="6">
-      <c r="A16" s="207" t="n"/>
-      <c r="B16" s="208" t="n"/>
-      <c r="C16" s="209" t="n"/>
-      <c r="D16" s="208" t="n"/>
-      <c r="E16" s="209" t="n"/>
-      <c r="F16" s="208" t="n"/>
-      <c r="G16" s="209" t="n"/>
-      <c r="H16" s="208" t="n"/>
-      <c r="I16" s="209" t="n"/>
-      <c r="J16" s="208" t="n"/>
-      <c r="K16" s="209" t="n"/>
-      <c r="L16" s="208" t="n"/>
-      <c r="M16" s="207" t="n"/>
-      <c r="N16" s="208" t="n"/>
-      <c r="O16" s="210" t="n"/>
-      <c r="P16" s="209" t="n"/>
-      <c r="Q16" s="208" t="n"/>
-      <c r="R16" s="209" t="n"/>
-      <c r="S16" s="208" t="n"/>
-      <c r="T16" s="207" t="n"/>
-      <c r="U16" s="208" t="n"/>
-      <c r="V16" s="210" t="n"/>
-      <c r="W16" s="209" t="n"/>
-      <c r="X16" s="208" t="n"/>
-      <c r="Y16" s="210" t="n"/>
-      <c r="Z16" s="210" t="n"/>
-      <c r="AA16" s="211" t="n"/>
-      <c r="AB16" s="212" t="n"/>
-      <c r="AC16" s="210" t="n"/>
-      <c r="AD16" s="210" t="n"/>
-      <c r="AE16" s="210" t="n"/>
-      <c r="AF16" s="210" t="n"/>
-      <c r="AG16" s="210" t="n"/>
-      <c r="AH16" s="210" t="n"/>
-      <c r="AI16" s="210" t="n"/>
-      <c r="AJ16" s="210" t="n"/>
-      <c r="AK16" s="210" t="n"/>
-      <c r="AL16" s="211" t="n"/>
+      <c r="A16" s="209" t="n"/>
+      <c r="B16" s="210" t="n"/>
+      <c r="C16" s="211" t="n"/>
+      <c r="D16" s="210" t="n"/>
+      <c r="E16" s="211" t="n"/>
+      <c r="F16" s="210" t="n"/>
+      <c r="G16" s="211" t="n"/>
+      <c r="H16" s="210" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="210" t="n"/>
+      <c r="K16" s="211" t="n"/>
+      <c r="L16" s="210" t="n"/>
+      <c r="M16" s="209" t="n"/>
+      <c r="N16" s="210" t="n"/>
+      <c r="O16" s="212" t="n"/>
+      <c r="P16" s="211" t="n"/>
+      <c r="Q16" s="210" t="n"/>
+      <c r="R16" s="211" t="n"/>
+      <c r="S16" s="210" t="n"/>
+      <c r="T16" s="209" t="n"/>
+      <c r="U16" s="210" t="n"/>
+      <c r="V16" s="212" t="n"/>
+      <c r="W16" s="211" t="n"/>
+      <c r="X16" s="210" t="n"/>
+      <c r="Y16" s="212" t="n"/>
+      <c r="Z16" s="212" t="n"/>
+      <c r="AA16" s="213" t="n"/>
+      <c r="AB16" s="214" t="n"/>
+      <c r="AC16" s="212" t="n"/>
+      <c r="AD16" s="212" t="n"/>
+      <c r="AE16" s="212" t="n"/>
+      <c r="AF16" s="212" t="n"/>
+      <c r="AG16" s="212" t="n"/>
+      <c r="AH16" s="212" t="n"/>
+      <c r="AI16" s="212" t="n"/>
+      <c r="AJ16" s="212" t="n"/>
+      <c r="AK16" s="212" t="n"/>
+      <c r="AL16" s="213" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
       <c r="B17" s="199" t="n"/>
-      <c r="C17" s="205" t="n"/>
+      <c r="C17" s="206" t="n"/>
       <c r="D17" s="199" t="n"/>
-      <c r="E17" s="205" t="n"/>
+      <c r="E17" s="206" t="n"/>
       <c r="F17" s="199" t="n"/>
-      <c r="G17" s="205" t="n"/>
+      <c r="G17" s="206" t="n"/>
       <c r="H17" s="199" t="n"/>
-      <c r="I17" s="205" t="n"/>
+      <c r="I17" s="206" t="n"/>
       <c r="J17" s="199" t="n"/>
-      <c r="K17" s="205" t="n"/>
+      <c r="K17" s="206" t="n"/>
       <c r="L17" s="199" t="n"/>
       <c r="M17" s="198" t="n"/>
       <c r="N17" s="199" t="n"/>
-      <c r="O17" s="213" t="n"/>
-      <c r="P17" s="205" t="n"/>
+      <c r="O17" s="215" t="n"/>
+      <c r="P17" s="206" t="n"/>
       <c r="Q17" s="199" t="n"/>
-      <c r="R17" s="205" t="n"/>
+      <c r="R17" s="206" t="n"/>
       <c r="S17" s="199" t="n"/>
       <c r="T17" s="198" t="n"/>
       <c r="U17" s="199" t="n"/>
-      <c r="V17" s="213" t="n"/>
-      <c r="W17" s="205" t="n"/>
+      <c r="V17" s="215" t="n"/>
+      <c r="W17" s="206" t="n"/>
       <c r="X17" s="199" t="n"/>
-      <c r="Y17" s="213" t="n"/>
-      <c r="Z17" s="213" t="n"/>
-      <c r="AA17" s="214" t="n"/>
-      <c r="AB17" s="215" t="n"/>
-      <c r="AC17" s="213" t="n"/>
-      <c r="AD17" s="213" t="n"/>
-      <c r="AE17" s="213" t="n"/>
-      <c r="AF17" s="213" t="n"/>
-      <c r="AG17" s="213" t="n"/>
-      <c r="AH17" s="213" t="n"/>
-      <c r="AI17" s="213" t="n"/>
-      <c r="AJ17" s="213" t="n"/>
-      <c r="AK17" s="213" t="n"/>
-      <c r="AL17" s="214" t="n"/>
+      <c r="Y17" s="215" t="n"/>
+      <c r="Z17" s="215" t="n"/>
+      <c r="AA17" s="216" t="n"/>
+      <c r="AB17" s="217" t="n"/>
+      <c r="AC17" s="215" t="n"/>
+      <c r="AD17" s="215" t="n"/>
+      <c r="AE17" s="215" t="n"/>
+      <c r="AF17" s="215" t="n"/>
+      <c r="AG17" s="215" t="n"/>
+      <c r="AH17" s="215" t="n"/>
+      <c r="AI17" s="215" t="n"/>
+      <c r="AJ17" s="215" t="n"/>
+      <c r="AK17" s="215" t="n"/>
+      <c r="AL17" s="216" t="n"/>
     </row>
     <row r="18" ht="109.5" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -4011,8 +4034,8 @@
           <t>HEAD LAMP STAGE</t>
         </is>
       </c>
-      <c r="B18" s="206" t="n"/>
-      <c r="C18" s="216" t="inlineStr">
+      <c r="B18" s="207" t="n"/>
+      <c r="C18" s="218" t="inlineStr">
         <is>
           <t xml:space="preserve">Operation No: 
 Stage: 
@@ -4020,8 +4043,8 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="206" t="n"/>
-      <c r="E18" s="217" t="inlineStr">
+      <c r="D18" s="207" t="n"/>
+      <c r="E18" s="219" t="inlineStr">
         <is>
           <t>1 Man - Operator
 2.Machine-  
@@ -4035,8 +4058,8 @@
 6.Measurement- NA</t>
         </is>
       </c>
-      <c r="F18" s="206" t="n"/>
-      <c r="G18" s="218" t="inlineStr">
+      <c r="F18" s="207" t="n"/>
+      <c r="G18" s="220" t="inlineStr">
         <is>
           <t>Your Plant :
 To correctly install front grill fitment as per BIW design specifications.
@@ -4047,14 +4070,14 @@
 3. Provide vehicle styling and brand identity</t>
         </is>
       </c>
-      <c r="H18" s="206" t="n"/>
+      <c r="H18" s="207" t="n"/>
       <c r="I18" s="162" t="inlineStr">
         <is>
           <t>SELECTION OF PART AS PER MODEL</t>
         </is>
       </c>
-      <c r="J18" s="206" t="n"/>
-      <c r="K18" s="219" t="inlineStr">
+      <c r="J18" s="207" t="n"/>
+      <c r="K18" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Man: 
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
@@ -4071,7 +4094,7 @@
 </t>
         </is>
       </c>
-      <c r="L18" s="206" t="n"/>
+      <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -4085,7 +4108,7 @@
 3. Customer dissatisfaction</t>
         </is>
       </c>
-      <c r="N18" s="206" t="n"/>
+      <c r="N18" s="207" t="n"/>
       <c r="O18" s="162" t="n">
         <v>6</v>
       </c>
@@ -4094,7 +4117,7 @@
           <t>WRONG PART SELECTION</t>
         </is>
       </c>
-      <c r="Q18" s="206" t="n"/>
+      <c r="Q18" s="207" t="n"/>
       <c r="R18" s="155" t="n"/>
       <c r="S18" s="201" t="n"/>
       <c r="T18" s="156" t="n"/>
@@ -4102,14 +4125,14 @@
       <c r="V18" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="220" t="inlineStr">
+      <c r="W18" s="222" t="inlineStr">
         <is>
           <t>1. SELF CHECK, 
 2. CHECKMAN CHECKING,
 3. VMS scanning system</t>
         </is>
       </c>
-      <c r="X18" s="206" t="n"/>
+      <c r="X18" s="207" t="n"/>
       <c r="Y18" s="162" t="n">
         <v>6</v>
       </c>
@@ -4129,21 +4152,21 @@
       <c r="AL18" s="35" t="n"/>
     </row>
     <row r="19" ht="207" customFormat="1" customHeight="1" s="8">
-      <c r="B19" s="208" t="n"/>
-      <c r="C19" s="209" t="n"/>
-      <c r="D19" s="208" t="n"/>
-      <c r="E19" s="209" t="n"/>
-      <c r="F19" s="208" t="n"/>
-      <c r="G19" s="209" t="n"/>
-      <c r="H19" s="208" t="n"/>
-      <c r="I19" s="205" t="n"/>
+      <c r="B19" s="210" t="n"/>
+      <c r="C19" s="211" t="n"/>
+      <c r="D19" s="210" t="n"/>
+      <c r="E19" s="211" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="211" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="206" t="n"/>
       <c r="J19" s="199" t="n"/>
-      <c r="K19" s="209" t="n"/>
-      <c r="L19" s="208" t="n"/>
-      <c r="M19" s="209" t="n"/>
-      <c r="N19" s="208" t="n"/>
-      <c r="O19" s="210" t="n"/>
-      <c r="P19" s="205" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="210" t="n"/>
+      <c r="M19" s="211" t="n"/>
+      <c r="N19" s="210" t="n"/>
+      <c r="O19" s="212" t="n"/>
+      <c r="P19" s="206" t="n"/>
       <c r="Q19" s="199" t="n"/>
       <c r="R19" s="43" t="inlineStr">
         <is>
@@ -4151,18 +4174,18 @@
 SEQUENCING WRONG</t>
         </is>
       </c>
-      <c r="S19" s="206" t="n"/>
+      <c r="S19" s="207" t="n"/>
       <c r="T19" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, PART TRACEABILITY, Sequencing part</t>
         </is>
       </c>
-      <c r="U19" s="206" t="n"/>
-      <c r="V19" s="210" t="n"/>
-      <c r="W19" s="209" t="n"/>
-      <c r="X19" s="208" t="n"/>
-      <c r="Y19" s="210" t="n"/>
-      <c r="Z19" s="210" t="n"/>
+      <c r="U19" s="207" t="n"/>
+      <c r="V19" s="212" t="n"/>
+      <c r="W19" s="211" t="n"/>
+      <c r="X19" s="210" t="n"/>
+      <c r="Y19" s="212" t="n"/>
+      <c r="Z19" s="212" t="n"/>
       <c r="AA19" s="162" t="n"/>
       <c r="AB19" s="162" t="n"/>
       <c r="AC19" s="45" t="n"/>
@@ -4174,39 +4197,39 @@
       <c r="AL19" s="35" t="n"/>
     </row>
     <row r="20" ht="126" customFormat="1" customHeight="1" s="8">
-      <c r="B20" s="208" t="n"/>
-      <c r="C20" s="209" t="n"/>
-      <c r="D20" s="208" t="n"/>
-      <c r="E20" s="209" t="n"/>
-      <c r="F20" s="208" t="n"/>
-      <c r="G20" s="209" t="n"/>
-      <c r="H20" s="208" t="n"/>
+      <c r="B20" s="210" t="n"/>
+      <c r="C20" s="211" t="n"/>
+      <c r="D20" s="210" t="n"/>
+      <c r="E20" s="211" t="n"/>
+      <c r="F20" s="210" t="n"/>
+      <c r="G20" s="211" t="n"/>
+      <c r="H20" s="210" t="n"/>
       <c r="I20" s="154" t="inlineStr">
         <is>
           <t>ENSURE PUSHPIN FITMENT</t>
         </is>
       </c>
-      <c r="J20" s="206" t="n"/>
-      <c r="K20" s="209" t="n"/>
-      <c r="L20" s="208" t="n"/>
-      <c r="M20" s="209" t="n"/>
-      <c r="N20" s="208" t="n"/>
-      <c r="O20" s="210" t="n"/>
+      <c r="J20" s="207" t="n"/>
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="210" t="n"/>
+      <c r="M20" s="211" t="n"/>
+      <c r="N20" s="210" t="n"/>
+      <c r="O20" s="212" t="n"/>
       <c r="P20" s="162" t="inlineStr">
         <is>
           <t>PUSHPIN MISSING</t>
         </is>
       </c>
-      <c r="Q20" s="206" t="n"/>
+      <c r="Q20" s="207" t="n"/>
       <c r="R20" s="155" t="n"/>
       <c r="S20" s="201" t="n"/>
       <c r="T20" s="156" t="n"/>
       <c r="U20" s="201" t="n"/>
-      <c r="V20" s="210" t="n"/>
-      <c r="W20" s="209" t="n"/>
-      <c r="X20" s="208" t="n"/>
-      <c r="Y20" s="210" t="n"/>
-      <c r="Z20" s="210" t="n"/>
+      <c r="V20" s="212" t="n"/>
+      <c r="W20" s="211" t="n"/>
+      <c r="X20" s="210" t="n"/>
+      <c r="Y20" s="212" t="n"/>
+      <c r="Z20" s="212" t="n"/>
       <c r="AA20" s="162" t="n"/>
       <c r="AB20" s="162" t="n"/>
       <c r="AC20" s="45" t="n"/>
@@ -4218,21 +4241,21 @@
       <c r="AL20" s="35" t="n"/>
     </row>
     <row r="21" ht="147" customFormat="1" customHeight="1" s="8">
-      <c r="B21" s="208" t="n"/>
-      <c r="C21" s="209" t="n"/>
-      <c r="D21" s="208" t="n"/>
-      <c r="E21" s="209" t="n"/>
-      <c r="F21" s="208" t="n"/>
-      <c r="G21" s="209" t="n"/>
-      <c r="H21" s="208" t="n"/>
-      <c r="I21" s="205" t="n"/>
+      <c r="B21" s="210" t="n"/>
+      <c r="C21" s="211" t="n"/>
+      <c r="D21" s="210" t="n"/>
+      <c r="E21" s="211" t="n"/>
+      <c r="F21" s="210" t="n"/>
+      <c r="G21" s="211" t="n"/>
+      <c r="H21" s="210" t="n"/>
+      <c r="I21" s="206" t="n"/>
       <c r="J21" s="199" t="n"/>
-      <c r="K21" s="209" t="n"/>
-      <c r="L21" s="208" t="n"/>
-      <c r="M21" s="205" t="n"/>
+      <c r="K21" s="211" t="n"/>
+      <c r="L21" s="210" t="n"/>
+      <c r="M21" s="206" t="n"/>
       <c r="N21" s="199" t="n"/>
-      <c r="O21" s="213" t="n"/>
-      <c r="P21" s="205" t="n"/>
+      <c r="O21" s="215" t="n"/>
+      <c r="P21" s="206" t="n"/>
       <c r="Q21" s="199" t="n"/>
       <c r="R21" s="43" t="inlineStr">
         <is>
@@ -4240,18 +4263,18 @@
 SEQUENCING WRONG</t>
         </is>
       </c>
-      <c r="S21" s="206" t="n"/>
+      <c r="S21" s="207" t="n"/>
       <c r="T21" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, PART TRACEABILITY, Sequencing part</t>
         </is>
       </c>
-      <c r="U21" s="206" t="n"/>
-      <c r="V21" s="213" t="n"/>
-      <c r="W21" s="205" t="n"/>
+      <c r="U21" s="207" t="n"/>
+      <c r="V21" s="215" t="n"/>
+      <c r="W21" s="206" t="n"/>
       <c r="X21" s="199" t="n"/>
-      <c r="Y21" s="213" t="n"/>
-      <c r="Z21" s="213" t="n"/>
+      <c r="Y21" s="215" t="n"/>
+      <c r="Z21" s="215" t="n"/>
       <c r="AA21" s="162" t="n"/>
       <c r="AB21" s="162" t="n"/>
       <c r="AC21" s="45" t="n"/>
@@ -4263,22 +4286,22 @@
       <c r="AL21" s="35" t="n"/>
     </row>
     <row r="22" ht="102" customFormat="1" customHeight="1" s="8">
-      <c r="B22" s="208" t="n"/>
-      <c r="C22" s="209" t="n"/>
-      <c r="D22" s="208" t="n"/>
-      <c r="E22" s="209" t="n"/>
-      <c r="F22" s="208" t="n"/>
-      <c r="G22" s="209" t="n"/>
-      <c r="H22" s="208" t="n"/>
+      <c r="B22" s="210" t="n"/>
+      <c r="C22" s="211" t="n"/>
+      <c r="D22" s="210" t="n"/>
+      <c r="E22" s="211" t="n"/>
+      <c r="F22" s="210" t="n"/>
+      <c r="G22" s="211" t="n"/>
+      <c r="H22" s="210" t="n"/>
       <c r="I22" s="154" t="inlineStr">
         <is>
           <t>ENSURE LOCKING OF CONNECTORS</t>
         </is>
       </c>
-      <c r="J22" s="206" t="n"/>
-      <c r="K22" s="209" t="n"/>
-      <c r="L22" s="208" t="n"/>
-      <c r="M22" s="221" t="inlineStr">
+      <c r="J22" s="207" t="n"/>
+      <c r="K22" s="211" t="n"/>
+      <c r="L22" s="210" t="n"/>
+      <c r="M22" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. Wiring harness partially connected (loose fitment)
@@ -4292,7 +4315,7 @@
 4. Increased risk of accident</t>
         </is>
       </c>
-      <c r="N22" s="206" t="n"/>
+      <c r="N22" s="207" t="n"/>
       <c r="O22" s="146" t="n"/>
       <c r="P22" s="162" t="inlineStr">
         <is>
@@ -4300,7 +4323,7 @@
 POOR LOCKING</t>
         </is>
       </c>
-      <c r="Q22" s="206" t="n"/>
+      <c r="Q22" s="207" t="n"/>
       <c r="R22" s="155" t="n"/>
       <c r="S22" s="201" t="n"/>
       <c r="T22" s="156" t="n"/>
@@ -4321,37 +4344,37 @@
       <c r="AL22" s="35" t="n"/>
     </row>
     <row r="23" ht="189.95" customFormat="1" customHeight="1" s="14">
-      <c r="B23" s="208" t="n"/>
-      <c r="C23" s="209" t="n"/>
-      <c r="D23" s="208" t="n"/>
-      <c r="E23" s="209" t="n"/>
-      <c r="F23" s="208" t="n"/>
-      <c r="G23" s="209" t="n"/>
-      <c r="H23" s="208" t="n"/>
-      <c r="I23" s="205" t="n"/>
+      <c r="B23" s="210" t="n"/>
+      <c r="C23" s="211" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="211" t="n"/>
+      <c r="F23" s="210" t="n"/>
+      <c r="G23" s="211" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="206" t="n"/>
       <c r="J23" s="199" t="n"/>
-      <c r="K23" s="209" t="n"/>
-      <c r="L23" s="208" t="n"/>
-      <c r="M23" s="209" t="n"/>
-      <c r="N23" s="208" t="n"/>
+      <c r="K23" s="211" t="n"/>
+      <c r="L23" s="210" t="n"/>
+      <c r="M23" s="211" t="n"/>
+      <c r="N23" s="210" t="n"/>
       <c r="O23" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="P23" s="205" t="n"/>
+      <c r="P23" s="206" t="n"/>
       <c r="Q23" s="199" t="n"/>
       <c r="R23" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator, Connector not fully seated by operator</t>
         </is>
       </c>
-      <c r="S23" s="206" t="n"/>
+      <c r="S23" s="207" t="n"/>
       <c r="T23" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U23" s="206" t="n"/>
+      <c r="U23" s="207" t="n"/>
       <c r="V23" s="162" t="n">
         <v>3</v>
       </c>
@@ -4361,7 +4384,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X23" s="206" t="n"/>
+      <c r="X23" s="207" t="n"/>
       <c r="Y23" s="45" t="n">
         <v>5</v>
       </c>
@@ -4384,39 +4407,39 @@
       <c r="AL23" s="10" t="n"/>
     </row>
     <row r="24" ht="118.5" customFormat="1" customHeight="1" s="14">
-      <c r="B24" s="208" t="n"/>
-      <c r="C24" s="209" t="n"/>
-      <c r="D24" s="208" t="n"/>
-      <c r="E24" s="209" t="n"/>
-      <c r="F24" s="208" t="n"/>
-      <c r="G24" s="209" t="n"/>
-      <c r="H24" s="208" t="n"/>
+      <c r="B24" s="210" t="n"/>
+      <c r="C24" s="211" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="211" t="n"/>
+      <c r="F24" s="210" t="n"/>
+      <c r="G24" s="211" t="n"/>
+      <c r="H24" s="210" t="n"/>
       <c r="I24" s="154" t="inlineStr">
         <is>
           <t>ALIGNMENT OF FRONT GRILL WITH BIW</t>
         </is>
       </c>
-      <c r="J24" s="206" t="n"/>
-      <c r="K24" s="209" t="n"/>
-      <c r="L24" s="208" t="n"/>
-      <c r="M24" s="209" t="n"/>
-      <c r="N24" s="208" t="n"/>
-      <c r="O24" s="210" t="n"/>
+      <c r="J24" s="207" t="n"/>
+      <c r="K24" s="211" t="n"/>
+      <c r="L24" s="210" t="n"/>
+      <c r="M24" s="211" t="n"/>
+      <c r="N24" s="210" t="n"/>
+      <c r="O24" s="212" t="n"/>
       <c r="P24" s="162" t="inlineStr">
         <is>
           <t>WRONG POSITIONING</t>
         </is>
       </c>
-      <c r="Q24" s="206" t="n"/>
+      <c r="Q24" s="207" t="n"/>
       <c r="R24" s="155" t="n"/>
       <c r="S24" s="201" t="n"/>
       <c r="T24" s="156" t="n"/>
       <c r="U24" s="201" t="n"/>
-      <c r="V24" s="210" t="n"/>
-      <c r="W24" s="209" t="n"/>
-      <c r="X24" s="208" t="n"/>
-      <c r="Y24" s="210" t="n"/>
-      <c r="Z24" s="210" t="n"/>
+      <c r="V24" s="212" t="n"/>
+      <c r="W24" s="211" t="n"/>
+      <c r="X24" s="210" t="n"/>
+      <c r="Y24" s="212" t="n"/>
+      <c r="Z24" s="212" t="n"/>
       <c r="AA24" s="17" t="n"/>
       <c r="AB24" s="16" t="n"/>
       <c r="AC24" s="12" t="n"/>
@@ -4431,40 +4454,40 @@
       <c r="AL24" s="10" t="n"/>
     </row>
     <row r="25" ht="236.1" customFormat="1" customHeight="1" s="14">
-      <c r="B25" s="208" t="n"/>
-      <c r="C25" s="209" t="n"/>
-      <c r="D25" s="208" t="n"/>
-      <c r="E25" s="209" t="n"/>
-      <c r="F25" s="208" t="n"/>
-      <c r="G25" s="209" t="n"/>
-      <c r="H25" s="208" t="n"/>
-      <c r="I25" s="205" t="n"/>
+      <c r="B25" s="210" t="n"/>
+      <c r="C25" s="211" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="211" t="n"/>
+      <c r="F25" s="210" t="n"/>
+      <c r="G25" s="211" t="n"/>
+      <c r="H25" s="210" t="n"/>
+      <c r="I25" s="206" t="n"/>
       <c r="J25" s="199" t="n"/>
-      <c r="K25" s="209" t="n"/>
-      <c r="L25" s="208" t="n"/>
-      <c r="M25" s="205" t="n"/>
+      <c r="K25" s="211" t="n"/>
+      <c r="L25" s="210" t="n"/>
+      <c r="M25" s="206" t="n"/>
       <c r="N25" s="199" t="n"/>
-      <c r="O25" s="210" t="n"/>
-      <c r="P25" s="205" t="n"/>
+      <c r="O25" s="212" t="n"/>
+      <c r="P25" s="206" t="n"/>
       <c r="Q25" s="199" t="n"/>
       <c r="R25" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator, Connector not fully seated by operator</t>
         </is>
       </c>
-      <c r="S25" s="206" t="n"/>
+      <c r="S25" s="207" t="n"/>
       <c r="T25" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U25" s="206" t="n"/>
-      <c r="V25" s="213" t="n"/>
-      <c r="W25" s="209" t="n"/>
-      <c r="X25" s="208" t="n"/>
-      <c r="Y25" s="210" t="n"/>
-      <c r="Z25" s="213" t="n"/>
+      <c r="U25" s="207" t="n"/>
+      <c r="V25" s="215" t="n"/>
+      <c r="W25" s="211" t="n"/>
+      <c r="X25" s="210" t="n"/>
+      <c r="Y25" s="212" t="n"/>
+      <c r="Z25" s="215" t="n"/>
       <c r="AA25" s="15" t="n"/>
       <c r="AB25" s="16" t="n"/>
       <c r="AC25" s="12" t="n"/>
@@ -4479,22 +4502,22 @@
       <c r="AL25" s="10" t="n"/>
     </row>
     <row r="26" ht="135.75" customFormat="1" customHeight="1" s="14">
-      <c r="B26" s="208" t="n"/>
-      <c r="C26" s="209" t="n"/>
-      <c r="D26" s="208" t="n"/>
-      <c r="E26" s="209" t="n"/>
-      <c r="F26" s="208" t="n"/>
-      <c r="G26" s="209" t="n"/>
-      <c r="H26" s="208" t="n"/>
-      <c r="I26" s="223" t="inlineStr">
+      <c r="B26" s="210" t="n"/>
+      <c r="C26" s="211" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="210" t="n"/>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="210" t="n"/>
+      <c r="I26" s="225" t="inlineStr">
         <is>
           <t>PROPER TIGHTENING OF JOINT</t>
         </is>
       </c>
-      <c r="J26" s="206" t="n"/>
-      <c r="K26" s="209" t="n"/>
-      <c r="L26" s="208" t="n"/>
-      <c r="M26" s="221" t="inlineStr">
+      <c r="J26" s="207" t="n"/>
+      <c r="K26" s="211" t="n"/>
+      <c r="L26" s="210" t="n"/>
+      <c r="M26" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
@@ -4508,21 +4531,21 @@
 4. Rattling or vibration noise during driving</t>
         </is>
       </c>
-      <c r="N26" s="206" t="n"/>
+      <c r="N26" s="207" t="n"/>
       <c r="O26" s="146" t="n"/>
       <c r="P26" s="162" t="inlineStr">
         <is>
           <t>OPERATOR FAILED TO FIT BOLTS</t>
         </is>
       </c>
-      <c r="Q26" s="206" t="n"/>
+      <c r="Q26" s="207" t="n"/>
       <c r="R26" s="155" t="n"/>
       <c r="S26" s="201" t="n"/>
       <c r="T26" s="156" t="n"/>
       <c r="U26" s="201" t="n"/>
       <c r="V26" s="45" t="n"/>
-      <c r="W26" s="209" t="n"/>
-      <c r="X26" s="208" t="n"/>
+      <c r="W26" s="211" t="n"/>
+      <c r="X26" s="210" t="n"/>
       <c r="Y26" s="146" t="n"/>
       <c r="Z26" s="186" t="n"/>
       <c r="AA26" s="15" t="n"/>
@@ -4539,41 +4562,41 @@
       <c r="AL26" s="10" t="n"/>
     </row>
     <row r="27" ht="135" customFormat="1" customHeight="1" s="13">
-      <c r="B27" s="208" t="n"/>
-      <c r="C27" s="209" t="n"/>
-      <c r="D27" s="208" t="n"/>
-      <c r="E27" s="209" t="n"/>
-      <c r="F27" s="208" t="n"/>
-      <c r="G27" s="209" t="n"/>
-      <c r="H27" s="208" t="n"/>
-      <c r="I27" s="209" t="n"/>
-      <c r="J27" s="208" t="n"/>
-      <c r="K27" s="209" t="n"/>
-      <c r="L27" s="208" t="n"/>
-      <c r="M27" s="209" t="n"/>
-      <c r="N27" s="208" t="n"/>
+      <c r="B27" s="210" t="n"/>
+      <c r="C27" s="211" t="n"/>
+      <c r="D27" s="210" t="n"/>
+      <c r="E27" s="211" t="n"/>
+      <c r="F27" s="210" t="n"/>
+      <c r="G27" s="211" t="n"/>
+      <c r="H27" s="210" t="n"/>
+      <c r="I27" s="211" t="n"/>
+      <c r="J27" s="210" t="n"/>
+      <c r="K27" s="211" t="n"/>
+      <c r="L27" s="210" t="n"/>
+      <c r="M27" s="211" t="n"/>
+      <c r="N27" s="210" t="n"/>
       <c r="O27" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="P27" s="205" t="n"/>
+      <c r="P27" s="206" t="n"/>
       <c r="Q27" s="199" t="n"/>
       <c r="R27" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator, Connector not fully seated by operator</t>
         </is>
       </c>
-      <c r="S27" s="206" t="n"/>
+      <c r="S27" s="207" t="n"/>
       <c r="T27" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U27" s="206" t="n"/>
+      <c r="U27" s="207" t="n"/>
       <c r="V27" s="162" t="n">
         <v>3</v>
       </c>
-      <c r="W27" s="205" t="n"/>
+      <c r="W27" s="206" t="n"/>
       <c r="X27" s="199" t="n"/>
       <c r="Y27" s="162" t="n">
         <v>5</v>
@@ -4594,20 +4617,20 @@
       <c r="AL27" s="10" t="n"/>
     </row>
     <row r="28" ht="151.5" customFormat="1" customHeight="1" s="13">
-      <c r="B28" s="208" t="n"/>
-      <c r="C28" s="209" t="n"/>
-      <c r="D28" s="208" t="n"/>
-      <c r="E28" s="209" t="n"/>
-      <c r="F28" s="208" t="n"/>
-      <c r="G28" s="209" t="n"/>
-      <c r="H28" s="208" t="n"/>
-      <c r="I28" s="209" t="n"/>
-      <c r="J28" s="208" t="n"/>
-      <c r="K28" s="209" t="n"/>
-      <c r="L28" s="208" t="n"/>
-      <c r="M28" s="209" t="n"/>
-      <c r="N28" s="208" t="n"/>
-      <c r="O28" s="210" t="n"/>
+      <c r="B28" s="210" t="n"/>
+      <c r="C28" s="211" t="n"/>
+      <c r="D28" s="210" t="n"/>
+      <c r="E28" s="211" t="n"/>
+      <c r="F28" s="210" t="n"/>
+      <c r="G28" s="211" t="n"/>
+      <c r="H28" s="210" t="n"/>
+      <c r="I28" s="211" t="n"/>
+      <c r="J28" s="210" t="n"/>
+      <c r="K28" s="211" t="n"/>
+      <c r="L28" s="210" t="n"/>
+      <c r="M28" s="211" t="n"/>
+      <c r="N28" s="210" t="n"/>
+      <c r="O28" s="212" t="n"/>
       <c r="P28" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED-UNDER TORQUE</t>
@@ -4619,14 +4642,14 @@
           <t>SOS not followed by operator or CALIBRATION SET VALUE IS WRONG</t>
         </is>
       </c>
-      <c r="S28" s="206" t="n"/>
+      <c r="S28" s="207" t="n"/>
       <c r="T28" s="155" t="inlineStr">
         <is>
           <t>DEDICATED TOOLS FOR SPECIFIED TORQUE AND LABELS ON THE TOOL</t>
         </is>
       </c>
-      <c r="U28" s="206" t="n"/>
-      <c r="V28" s="210" t="n"/>
+      <c r="U28" s="207" t="n"/>
+      <c r="V28" s="212" t="n"/>
       <c r="W28" s="162" t="inlineStr">
         <is>
           <t>SELF CHECK,
@@ -4634,9 +4657,9 @@
 CALIBRATION RECORD</t>
         </is>
       </c>
-      <c r="X28" s="206" t="n"/>
-      <c r="Y28" s="210" t="n"/>
-      <c r="Z28" s="210" t="n"/>
+      <c r="X28" s="207" t="n"/>
+      <c r="Y28" s="212" t="n"/>
+      <c r="Z28" s="212" t="n"/>
       <c r="AA28" s="17" t="n"/>
       <c r="AB28" s="9" t="n"/>
       <c r="AC28" s="12" t="n"/>
@@ -4648,35 +4671,35 @@
       <c r="AL28" s="10" t="n"/>
     </row>
     <row r="29" ht="128.45" customFormat="1" customHeight="1" s="13">
-      <c r="B29" s="208" t="n"/>
-      <c r="C29" s="209" t="n"/>
-      <c r="D29" s="208" t="n"/>
-      <c r="E29" s="209" t="n"/>
-      <c r="F29" s="208" t="n"/>
-      <c r="G29" s="209" t="n"/>
-      <c r="H29" s="208" t="n"/>
-      <c r="I29" s="205" t="n"/>
+      <c r="B29" s="210" t="n"/>
+      <c r="C29" s="211" t="n"/>
+      <c r="D29" s="210" t="n"/>
+      <c r="E29" s="211" t="n"/>
+      <c r="F29" s="210" t="n"/>
+      <c r="G29" s="211" t="n"/>
+      <c r="H29" s="210" t="n"/>
+      <c r="I29" s="206" t="n"/>
       <c r="J29" s="199" t="n"/>
-      <c r="K29" s="209" t="n"/>
-      <c r="L29" s="208" t="n"/>
-      <c r="M29" s="205" t="n"/>
+      <c r="K29" s="211" t="n"/>
+      <c r="L29" s="210" t="n"/>
+      <c r="M29" s="206" t="n"/>
       <c r="N29" s="199" t="n"/>
-      <c r="O29" s="213" t="n"/>
+      <c r="O29" s="215" t="n"/>
       <c r="P29" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED - OVER TORQUE</t>
         </is>
       </c>
       <c r="Q29" s="201" t="n"/>
-      <c r="R29" s="205" t="n"/>
+      <c r="R29" s="206" t="n"/>
       <c r="S29" s="199" t="n"/>
-      <c r="T29" s="205" t="n"/>
+      <c r="T29" s="206" t="n"/>
       <c r="U29" s="199" t="n"/>
-      <c r="V29" s="213" t="n"/>
-      <c r="W29" s="205" t="n"/>
+      <c r="V29" s="215" t="n"/>
+      <c r="W29" s="206" t="n"/>
       <c r="X29" s="199" t="n"/>
-      <c r="Y29" s="213" t="n"/>
-      <c r="Z29" s="213" t="n"/>
+      <c r="Y29" s="215" t="n"/>
+      <c r="Z29" s="215" t="n"/>
       <c r="AA29" s="17" t="n"/>
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="12" t="n"/>
@@ -5271,7 +5294,7 @@
       <c r="D14" s="195" t="n"/>
       <c r="E14" s="195" t="n"/>
       <c r="F14" s="199" t="n"/>
-      <c r="G14" s="205" t="n"/>
+      <c r="G14" s="206" t="n"/>
       <c r="H14" s="195" t="n"/>
       <c r="I14" s="195" t="n"/>
       <c r="J14" s="195" t="n"/>
@@ -5312,47 +5335,47 @@
 Name of Process</t>
         </is>
       </c>
-      <c r="B15" s="206" t="n"/>
+      <c r="B15" s="207" t="n"/>
       <c r="C15" s="96" t="inlineStr">
         <is>
           <t>2. Process Step Station No. and Name of
 Focus Element</t>
         </is>
       </c>
-      <c r="D15" s="206" t="n"/>
+      <c r="D15" s="207" t="n"/>
       <c r="E15" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Process Work Element </t>
         </is>
       </c>
-      <c r="F15" s="206" t="n"/>
+      <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
           <t>1. Function of the Process Item Function of System, Subsystem,
 Part Element or Process</t>
         </is>
       </c>
-      <c r="H15" s="206" t="n"/>
+      <c r="H15" s="207" t="n"/>
       <c r="I15" s="96" t="inlineStr">
         <is>
           <t>2. Function of the Process Step and Product Characteristic
 (Quantitative value is optional)</t>
         </is>
       </c>
-      <c r="J15" s="206" t="n"/>
+      <c r="J15" s="207" t="n"/>
       <c r="K15" s="99" t="inlineStr">
         <is>
           <t>3. Function of the Process Work Element and Process
 Characteristic</t>
         </is>
       </c>
-      <c r="L15" s="206" t="n"/>
+      <c r="L15" s="207" t="n"/>
       <c r="M15" s="91" t="inlineStr">
         <is>
           <t>1. Failure Effects (FE) to the Next Higher Level Element and/or End User</t>
         </is>
       </c>
-      <c r="N15" s="206" t="n"/>
+      <c r="N15" s="207" t="n"/>
       <c r="O15" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Severity (S) of FE
@@ -5365,19 +5388,19 @@
 Focus Element</t>
         </is>
       </c>
-      <c r="Q15" s="206" t="n"/>
+      <c r="Q15" s="207" t="n"/>
       <c r="R15" s="99" t="inlineStr">
         <is>
           <t>3. Failure Cause (FC) of the Work Element</t>
         </is>
       </c>
-      <c r="S15" s="206" t="n"/>
+      <c r="S15" s="207" t="n"/>
       <c r="T15" s="141" t="inlineStr">
         <is>
           <t>Current Prevention Control (PC) of FC</t>
         </is>
       </c>
-      <c r="U15" s="206" t="n"/>
+      <c r="U15" s="207" t="n"/>
       <c r="V15" s="109" t="inlineStr">
         <is>
           <t>Occurrence (O) of FC</t>
@@ -5388,7 +5411,7 @@
           <t>Current Detection Controls (DC) of FC or FM</t>
         </is>
       </c>
-      <c r="X15" s="206" t="n"/>
+      <c r="X15" s="207" t="n"/>
       <c r="Y15" s="109" t="inlineStr">
         <is>
           <t>Detection (D) of FC/FM</t>
@@ -5462,84 +5485,84 @@
       </c>
     </row>
     <row r="16" ht="22.5" customFormat="1" customHeight="1" s="6">
-      <c r="A16" s="207" t="n"/>
-      <c r="B16" s="208" t="n"/>
-      <c r="C16" s="209" t="n"/>
-      <c r="D16" s="208" t="n"/>
-      <c r="E16" s="209" t="n"/>
-      <c r="F16" s="208" t="n"/>
-      <c r="G16" s="209" t="n"/>
-      <c r="H16" s="208" t="n"/>
-      <c r="I16" s="209" t="n"/>
-      <c r="J16" s="208" t="n"/>
-      <c r="K16" s="209" t="n"/>
-      <c r="L16" s="208" t="n"/>
-      <c r="M16" s="207" t="n"/>
-      <c r="N16" s="208" t="n"/>
-      <c r="O16" s="210" t="n"/>
-      <c r="P16" s="209" t="n"/>
-      <c r="Q16" s="208" t="n"/>
-      <c r="R16" s="209" t="n"/>
-      <c r="S16" s="208" t="n"/>
-      <c r="T16" s="207" t="n"/>
-      <c r="U16" s="208" t="n"/>
-      <c r="V16" s="210" t="n"/>
-      <c r="W16" s="209" t="n"/>
-      <c r="X16" s="208" t="n"/>
-      <c r="Y16" s="210" t="n"/>
-      <c r="Z16" s="210" t="n"/>
-      <c r="AA16" s="211" t="n"/>
-      <c r="AB16" s="212" t="n"/>
-      <c r="AC16" s="210" t="n"/>
-      <c r="AD16" s="210" t="n"/>
-      <c r="AE16" s="210" t="n"/>
-      <c r="AF16" s="210" t="n"/>
-      <c r="AG16" s="210" t="n"/>
-      <c r="AH16" s="210" t="n"/>
-      <c r="AI16" s="210" t="n"/>
-      <c r="AJ16" s="210" t="n"/>
-      <c r="AK16" s="210" t="n"/>
-      <c r="AL16" s="211" t="n"/>
+      <c r="A16" s="209" t="n"/>
+      <c r="B16" s="210" t="n"/>
+      <c r="C16" s="211" t="n"/>
+      <c r="D16" s="210" t="n"/>
+      <c r="E16" s="211" t="n"/>
+      <c r="F16" s="210" t="n"/>
+      <c r="G16" s="211" t="n"/>
+      <c r="H16" s="210" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="210" t="n"/>
+      <c r="K16" s="211" t="n"/>
+      <c r="L16" s="210" t="n"/>
+      <c r="M16" s="209" t="n"/>
+      <c r="N16" s="210" t="n"/>
+      <c r="O16" s="212" t="n"/>
+      <c r="P16" s="211" t="n"/>
+      <c r="Q16" s="210" t="n"/>
+      <c r="R16" s="211" t="n"/>
+      <c r="S16" s="210" t="n"/>
+      <c r="T16" s="209" t="n"/>
+      <c r="U16" s="210" t="n"/>
+      <c r="V16" s="212" t="n"/>
+      <c r="W16" s="211" t="n"/>
+      <c r="X16" s="210" t="n"/>
+      <c r="Y16" s="212" t="n"/>
+      <c r="Z16" s="212" t="n"/>
+      <c r="AA16" s="213" t="n"/>
+      <c r="AB16" s="214" t="n"/>
+      <c r="AC16" s="212" t="n"/>
+      <c r="AD16" s="212" t="n"/>
+      <c r="AE16" s="212" t="n"/>
+      <c r="AF16" s="212" t="n"/>
+      <c r="AG16" s="212" t="n"/>
+      <c r="AH16" s="212" t="n"/>
+      <c r="AI16" s="212" t="n"/>
+      <c r="AJ16" s="212" t="n"/>
+      <c r="AK16" s="212" t="n"/>
+      <c r="AL16" s="213" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
       <c r="B17" s="199" t="n"/>
-      <c r="C17" s="205" t="n"/>
+      <c r="C17" s="206" t="n"/>
       <c r="D17" s="199" t="n"/>
-      <c r="E17" s="205" t="n"/>
+      <c r="E17" s="206" t="n"/>
       <c r="F17" s="199" t="n"/>
-      <c r="G17" s="205" t="n"/>
+      <c r="G17" s="206" t="n"/>
       <c r="H17" s="199" t="n"/>
-      <c r="I17" s="205" t="n"/>
+      <c r="I17" s="206" t="n"/>
       <c r="J17" s="199" t="n"/>
-      <c r="K17" s="205" t="n"/>
+      <c r="K17" s="206" t="n"/>
       <c r="L17" s="199" t="n"/>
       <c r="M17" s="198" t="n"/>
       <c r="N17" s="199" t="n"/>
-      <c r="O17" s="213" t="n"/>
-      <c r="P17" s="205" t="n"/>
+      <c r="O17" s="215" t="n"/>
+      <c r="P17" s="206" t="n"/>
       <c r="Q17" s="199" t="n"/>
-      <c r="R17" s="205" t="n"/>
+      <c r="R17" s="206" t="n"/>
       <c r="S17" s="199" t="n"/>
       <c r="T17" s="198" t="n"/>
       <c r="U17" s="199" t="n"/>
-      <c r="V17" s="213" t="n"/>
-      <c r="W17" s="205" t="n"/>
+      <c r="V17" s="215" t="n"/>
+      <c r="W17" s="206" t="n"/>
       <c r="X17" s="199" t="n"/>
-      <c r="Y17" s="213" t="n"/>
-      <c r="Z17" s="213" t="n"/>
-      <c r="AA17" s="214" t="n"/>
-      <c r="AB17" s="215" t="n"/>
-      <c r="AC17" s="213" t="n"/>
-      <c r="AD17" s="213" t="n"/>
-      <c r="AE17" s="213" t="n"/>
-      <c r="AF17" s="213" t="n"/>
-      <c r="AG17" s="213" t="n"/>
-      <c r="AH17" s="213" t="n"/>
-      <c r="AI17" s="213" t="n"/>
-      <c r="AJ17" s="213" t="n"/>
-      <c r="AK17" s="213" t="n"/>
-      <c r="AL17" s="214" t="n"/>
+      <c r="Y17" s="215" t="n"/>
+      <c r="Z17" s="215" t="n"/>
+      <c r="AA17" s="216" t="n"/>
+      <c r="AB17" s="217" t="n"/>
+      <c r="AC17" s="215" t="n"/>
+      <c r="AD17" s="215" t="n"/>
+      <c r="AE17" s="215" t="n"/>
+      <c r="AF17" s="215" t="n"/>
+      <c r="AG17" s="215" t="n"/>
+      <c r="AH17" s="215" t="n"/>
+      <c r="AI17" s="215" t="n"/>
+      <c r="AJ17" s="215" t="n"/>
+      <c r="AK17" s="215" t="n"/>
+      <c r="AL17" s="216" t="n"/>
     </row>
     <row r="18" ht="107.25" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -5547,8 +5570,8 @@
           <t>HEAD LAMP STAGE</t>
         </is>
       </c>
-      <c r="B18" s="206" t="n"/>
-      <c r="C18" s="216" t="inlineStr">
+      <c r="B18" s="207" t="n"/>
+      <c r="C18" s="218" t="inlineStr">
         <is>
           <t xml:space="preserve">Operation No: 
 Stage: 
@@ -5556,8 +5579,8 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="206" t="n"/>
-      <c r="E18" s="217" t="inlineStr">
+      <c r="D18" s="207" t="n"/>
+      <c r="E18" s="219" t="inlineStr">
         <is>
           <t>1 Man - Operator
 2.Machine-  
@@ -5570,8 +5593,8 @@
 6.Measurement- NA</t>
         </is>
       </c>
-      <c r="F18" s="206" t="n"/>
-      <c r="G18" s="218" t="inlineStr">
+      <c r="F18" s="207" t="n"/>
+      <c r="G18" s="220" t="inlineStr">
         <is>
           <t>Your Plant :
 To correctly install front grill fitment as per BIW design specifications.
@@ -5582,14 +5605,14 @@
 3. Provide vehicle styling and brand identity</t>
         </is>
       </c>
-      <c r="H18" s="206" t="n"/>
+      <c r="H18" s="207" t="n"/>
       <c r="I18" s="162" t="inlineStr">
         <is>
           <t>SELECTION OF PART AS PER MODEL</t>
         </is>
       </c>
-      <c r="J18" s="206" t="n"/>
-      <c r="K18" s="219" t="inlineStr">
+      <c r="J18" s="207" t="n"/>
+      <c r="K18" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Man: 
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
@@ -5605,7 +5628,7 @@
 </t>
         </is>
       </c>
-      <c r="L18" s="206" t="n"/>
+      <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -5619,7 +5642,7 @@
 3. Bad appereance of vehicle</t>
         </is>
       </c>
-      <c r="N18" s="206" t="n"/>
+      <c r="N18" s="207" t="n"/>
       <c r="O18" s="162" t="n">
         <v>6</v>
       </c>
@@ -5628,7 +5651,7 @@
           <t>WRONG PART SELECTION</t>
         </is>
       </c>
-      <c r="Q18" s="206" t="n"/>
+      <c r="Q18" s="207" t="n"/>
       <c r="R18" s="155" t="n"/>
       <c r="S18" s="201" t="n"/>
       <c r="T18" s="156" t="n"/>
@@ -5643,7 +5666,7 @@
 3. VMS scanning system</t>
         </is>
       </c>
-      <c r="X18" s="206" t="n"/>
+      <c r="X18" s="207" t="n"/>
       <c r="Y18" s="162" t="n">
         <v>6</v>
       </c>
@@ -5663,21 +5686,21 @@
       <c r="AL18" s="35" t="n"/>
     </row>
     <row r="19" ht="136.5" customFormat="1" customHeight="1" s="8">
-      <c r="B19" s="208" t="n"/>
-      <c r="C19" s="209" t="n"/>
-      <c r="D19" s="208" t="n"/>
-      <c r="E19" s="209" t="n"/>
-      <c r="F19" s="208" t="n"/>
-      <c r="G19" s="209" t="n"/>
-      <c r="H19" s="208" t="n"/>
-      <c r="I19" s="205" t="n"/>
+      <c r="B19" s="210" t="n"/>
+      <c r="C19" s="211" t="n"/>
+      <c r="D19" s="210" t="n"/>
+      <c r="E19" s="211" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="211" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="206" t="n"/>
       <c r="J19" s="199" t="n"/>
-      <c r="K19" s="209" t="n"/>
-      <c r="L19" s="208" t="n"/>
-      <c r="M19" s="209" t="n"/>
-      <c r="N19" s="208" t="n"/>
-      <c r="O19" s="210" t="n"/>
-      <c r="P19" s="205" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="210" t="n"/>
+      <c r="M19" s="211" t="n"/>
+      <c r="N19" s="210" t="n"/>
+      <c r="O19" s="212" t="n"/>
+      <c r="P19" s="206" t="n"/>
       <c r="Q19" s="199" t="n"/>
       <c r="R19" s="43" t="inlineStr">
         <is>
@@ -5685,14 +5708,14 @@
 SEQUENCING WRONG</t>
         </is>
       </c>
-      <c r="S19" s="206" t="n"/>
+      <c r="S19" s="207" t="n"/>
       <c r="T19" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, PART TRACEABILITY, Sequencing part</t>
         </is>
       </c>
-      <c r="U19" s="206" t="n"/>
-      <c r="V19" s="210" t="n"/>
+      <c r="U19" s="207" t="n"/>
+      <c r="V19" s="212" t="n"/>
       <c r="W19" s="45" t="inlineStr">
         <is>
           <t>1. SELF CHECK, 
@@ -5700,9 +5723,9 @@
 3. VMS scanning system</t>
         </is>
       </c>
-      <c r="X19" s="206" t="n"/>
-      <c r="Y19" s="210" t="n"/>
-      <c r="Z19" s="210" t="n"/>
+      <c r="X19" s="207" t="n"/>
+      <c r="Y19" s="212" t="n"/>
+      <c r="Z19" s="212" t="n"/>
       <c r="AA19" s="162" t="n"/>
       <c r="AB19" s="162" t="n"/>
       <c r="AC19" s="45" t="n"/>
@@ -5714,35 +5737,35 @@
       <c r="AL19" s="35" t="n"/>
     </row>
     <row r="20" ht="145.5" customFormat="1" customHeight="1" s="8">
-      <c r="B20" s="208" t="n"/>
-      <c r="C20" s="209" t="n"/>
-      <c r="D20" s="208" t="n"/>
-      <c r="E20" s="209" t="n"/>
-      <c r="F20" s="208" t="n"/>
-      <c r="G20" s="209" t="n"/>
-      <c r="H20" s="208" t="n"/>
+      <c r="B20" s="210" t="n"/>
+      <c r="C20" s="211" t="n"/>
+      <c r="D20" s="210" t="n"/>
+      <c r="E20" s="211" t="n"/>
+      <c r="F20" s="210" t="n"/>
+      <c r="G20" s="211" t="n"/>
+      <c r="H20" s="210" t="n"/>
       <c r="I20" s="154" t="inlineStr">
         <is>
           <t>ENSURE PUSHPIN FITMENT</t>
         </is>
       </c>
-      <c r="J20" s="206" t="n"/>
-      <c r="K20" s="209" t="n"/>
-      <c r="L20" s="208" t="n"/>
-      <c r="M20" s="205" t="n"/>
+      <c r="J20" s="207" t="n"/>
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="210" t="n"/>
+      <c r="M20" s="206" t="n"/>
       <c r="N20" s="199" t="n"/>
-      <c r="O20" s="213" t="n"/>
+      <c r="O20" s="215" t="n"/>
       <c r="P20" s="162" t="inlineStr">
         <is>
           <t>PUSHPIN MISSING</t>
         </is>
       </c>
-      <c r="Q20" s="206" t="n"/>
+      <c r="Q20" s="207" t="n"/>
       <c r="R20" s="155" t="n"/>
       <c r="S20" s="201" t="n"/>
       <c r="T20" s="156" t="n"/>
       <c r="U20" s="201" t="n"/>
-      <c r="V20" s="213" t="n"/>
+      <c r="V20" s="215" t="n"/>
       <c r="W20" s="45" t="inlineStr">
         <is>
           <t>1. SELF CHECK, 
@@ -5750,9 +5773,9 @@
 3. VMS scanning system</t>
         </is>
       </c>
-      <c r="X20" s="206" t="n"/>
-      <c r="Y20" s="213" t="n"/>
-      <c r="Z20" s="213" t="n"/>
+      <c r="X20" s="207" t="n"/>
+      <c r="Y20" s="215" t="n"/>
+      <c r="Z20" s="215" t="n"/>
       <c r="AA20" s="162" t="n"/>
       <c r="AB20" s="162" t="n"/>
       <c r="AC20" s="45" t="n"/>
@@ -5764,17 +5787,17 @@
       <c r="AL20" s="35" t="n"/>
     </row>
     <row r="21" ht="112.5" customFormat="1" customHeight="1" s="14">
-      <c r="B21" s="208" t="n"/>
-      <c r="C21" s="209" t="n"/>
-      <c r="D21" s="208" t="n"/>
-      <c r="E21" s="209" t="n"/>
-      <c r="F21" s="208" t="n"/>
-      <c r="G21" s="209" t="n"/>
-      <c r="H21" s="208" t="n"/>
-      <c r="I21" s="205" t="n"/>
+      <c r="B21" s="210" t="n"/>
+      <c r="C21" s="211" t="n"/>
+      <c r="D21" s="210" t="n"/>
+      <c r="E21" s="211" t="n"/>
+      <c r="F21" s="210" t="n"/>
+      <c r="G21" s="211" t="n"/>
+      <c r="H21" s="210" t="n"/>
+      <c r="I21" s="206" t="n"/>
       <c r="J21" s="199" t="n"/>
-      <c r="K21" s="209" t="n"/>
-      <c r="L21" s="208" t="n"/>
+      <c r="K21" s="211" t="n"/>
+      <c r="L21" s="210" t="n"/>
       <c r="M21" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -5784,25 +5807,25 @@
 1. Water/dust ingress affecting part warrenty</t>
         </is>
       </c>
-      <c r="N21" s="206" t="n"/>
+      <c r="N21" s="207" t="n"/>
       <c r="O21" s="162" t="n">
         <v>6</v>
       </c>
-      <c r="P21" s="205" t="n"/>
+      <c r="P21" s="206" t="n"/>
       <c r="Q21" s="199" t="n"/>
       <c r="R21" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S21" s="206" t="n"/>
+      <c r="S21" s="207" t="n"/>
       <c r="T21" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U21" s="206" t="n"/>
+      <c r="U21" s="207" t="n"/>
       <c r="V21" s="162" t="n">
         <v>3</v>
       </c>
@@ -5812,7 +5835,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X21" s="206" t="n"/>
+      <c r="X21" s="207" t="n"/>
       <c r="Y21" s="162" t="n">
         <v>5</v>
       </c>
@@ -5835,44 +5858,44 @@
       <c r="AL21" s="10" t="n"/>
     </row>
     <row r="22" ht="101.25" customFormat="1" customHeight="1" s="14">
-      <c r="B22" s="208" t="n"/>
-      <c r="C22" s="209" t="n"/>
-      <c r="D22" s="208" t="n"/>
-      <c r="E22" s="209" t="n"/>
-      <c r="F22" s="208" t="n"/>
-      <c r="G22" s="209" t="n"/>
-      <c r="H22" s="208" t="n"/>
+      <c r="B22" s="210" t="n"/>
+      <c r="C22" s="211" t="n"/>
+      <c r="D22" s="210" t="n"/>
+      <c r="E22" s="211" t="n"/>
+      <c r="F22" s="210" t="n"/>
+      <c r="G22" s="211" t="n"/>
+      <c r="H22" s="210" t="n"/>
       <c r="I22" s="154" t="inlineStr">
         <is>
           <t>ALIGNMENT OF FRONT GRILL WITH BIW</t>
         </is>
       </c>
-      <c r="J22" s="206" t="n"/>
-      <c r="K22" s="209" t="n"/>
-      <c r="L22" s="208" t="n"/>
-      <c r="M22" s="209" t="n"/>
-      <c r="N22" s="208" t="n"/>
-      <c r="O22" s="210" t="n"/>
+      <c r="J22" s="207" t="n"/>
+      <c r="K22" s="211" t="n"/>
+      <c r="L22" s="210" t="n"/>
+      <c r="M22" s="211" t="n"/>
+      <c r="N22" s="210" t="n"/>
+      <c r="O22" s="212" t="n"/>
       <c r="P22" s="162" t="inlineStr">
         <is>
           <t>WRONG POSITIONING</t>
         </is>
       </c>
-      <c r="Q22" s="206" t="n"/>
+      <c r="Q22" s="207" t="n"/>
       <c r="R22" s="155" t="n"/>
       <c r="S22" s="201" t="n"/>
       <c r="T22" s="156" t="n"/>
       <c r="U22" s="201" t="n"/>
-      <c r="V22" s="210" t="n"/>
+      <c r="V22" s="212" t="n"/>
       <c r="W22" s="45" t="inlineStr">
         <is>
           <t>SELF CHECK ,
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X22" s="206" t="n"/>
-      <c r="Y22" s="210" t="n"/>
-      <c r="Z22" s="210" t="n"/>
+      <c r="X22" s="207" t="n"/>
+      <c r="Y22" s="212" t="n"/>
+      <c r="Z22" s="212" t="n"/>
       <c r="AA22" s="17" t="n"/>
       <c r="AB22" s="16" t="n"/>
       <c r="AC22" s="12" t="n"/>
@@ -5887,45 +5910,45 @@
       <c r="AL22" s="10" t="n"/>
     </row>
     <row r="23" ht="125.25" customFormat="1" customHeight="1" s="14">
-      <c r="B23" s="208" t="n"/>
-      <c r="C23" s="209" t="n"/>
-      <c r="D23" s="208" t="n"/>
-      <c r="E23" s="209" t="n"/>
-      <c r="F23" s="208" t="n"/>
-      <c r="G23" s="209" t="n"/>
-      <c r="H23" s="208" t="n"/>
-      <c r="I23" s="205" t="n"/>
+      <c r="B23" s="210" t="n"/>
+      <c r="C23" s="211" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="211" t="n"/>
+      <c r="F23" s="210" t="n"/>
+      <c r="G23" s="211" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="206" t="n"/>
       <c r="J23" s="199" t="n"/>
-      <c r="K23" s="209" t="n"/>
-      <c r="L23" s="208" t="n"/>
-      <c r="M23" s="205" t="n"/>
+      <c r="K23" s="211" t="n"/>
+      <c r="L23" s="210" t="n"/>
+      <c r="M23" s="206" t="n"/>
       <c r="N23" s="199" t="n"/>
-      <c r="O23" s="213" t="n"/>
-      <c r="P23" s="205" t="n"/>
+      <c r="O23" s="215" t="n"/>
+      <c r="P23" s="206" t="n"/>
       <c r="Q23" s="199" t="n"/>
       <c r="R23" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S23" s="206" t="n"/>
+      <c r="S23" s="207" t="n"/>
       <c r="T23" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U23" s="206" t="n"/>
-      <c r="V23" s="213" t="n"/>
+      <c r="U23" s="207" t="n"/>
+      <c r="V23" s="215" t="n"/>
       <c r="W23" s="45" t="inlineStr">
         <is>
           <t>SELF CHECK ,
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X23" s="206" t="n"/>
-      <c r="Y23" s="213" t="n"/>
-      <c r="Z23" s="213" t="n"/>
+      <c r="X23" s="207" t="n"/>
+      <c r="Y23" s="215" t="n"/>
+      <c r="Z23" s="215" t="n"/>
       <c r="AA23" s="15" t="n"/>
       <c r="AB23" s="16" t="n"/>
       <c r="AC23" s="12" t="n"/>
@@ -5940,22 +5963,22 @@
       <c r="AL23" s="10" t="n"/>
     </row>
     <row r="24" ht="93.75" customFormat="1" customHeight="1" s="14">
-      <c r="B24" s="208" t="n"/>
-      <c r="C24" s="209" t="n"/>
-      <c r="D24" s="208" t="n"/>
-      <c r="E24" s="209" t="n"/>
-      <c r="F24" s="208" t="n"/>
-      <c r="G24" s="209" t="n"/>
-      <c r="H24" s="208" t="n"/>
-      <c r="I24" s="223" t="inlineStr">
+      <c r="B24" s="210" t="n"/>
+      <c r="C24" s="211" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="211" t="n"/>
+      <c r="F24" s="210" t="n"/>
+      <c r="G24" s="211" t="n"/>
+      <c r="H24" s="210" t="n"/>
+      <c r="I24" s="225" t="inlineStr">
         <is>
           <t>PROPER TIGHTENING OF JOINT</t>
         </is>
       </c>
-      <c r="J24" s="206" t="n"/>
-      <c r="K24" s="209" t="n"/>
-      <c r="L24" s="208" t="n"/>
-      <c r="M24" s="221" t="inlineStr">
+      <c r="J24" s="207" t="n"/>
+      <c r="K24" s="211" t="n"/>
+      <c r="L24" s="210" t="n"/>
+      <c r="M24" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
@@ -5967,14 +5990,14 @@
 2. Rattling or vibration noise during driving</t>
         </is>
       </c>
-      <c r="N24" s="206" t="n"/>
+      <c r="N24" s="207" t="n"/>
       <c r="O24" s="46" t="n"/>
       <c r="P24" s="162" t="inlineStr">
         <is>
           <t>OPERATOR FAILED TO FIT BOLTS</t>
         </is>
       </c>
-      <c r="Q24" s="206" t="n"/>
+      <c r="Q24" s="207" t="n"/>
       <c r="R24" s="155" t="n"/>
       <c r="S24" s="201" t="n"/>
       <c r="T24" s="156" t="n"/>
@@ -5986,7 +6009,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X24" s="206" t="n"/>
+      <c r="X24" s="207" t="n"/>
       <c r="Y24" s="46" t="n"/>
       <c r="Z24" s="153" t="n"/>
       <c r="AA24" s="15" t="n"/>
@@ -6003,37 +6026,37 @@
       <c r="AL24" s="10" t="n"/>
     </row>
     <row r="25" ht="135" customFormat="1" customHeight="1" s="13">
-      <c r="B25" s="208" t="n"/>
-      <c r="C25" s="209" t="n"/>
-      <c r="D25" s="208" t="n"/>
-      <c r="E25" s="209" t="n"/>
-      <c r="F25" s="208" t="n"/>
-      <c r="G25" s="209" t="n"/>
-      <c r="H25" s="208" t="n"/>
-      <c r="I25" s="209" t="n"/>
-      <c r="J25" s="208" t="n"/>
-      <c r="K25" s="209" t="n"/>
-      <c r="L25" s="208" t="n"/>
-      <c r="M25" s="209" t="n"/>
-      <c r="N25" s="208" t="n"/>
+      <c r="B25" s="210" t="n"/>
+      <c r="C25" s="211" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="211" t="n"/>
+      <c r="F25" s="210" t="n"/>
+      <c r="G25" s="211" t="n"/>
+      <c r="H25" s="210" t="n"/>
+      <c r="I25" s="211" t="n"/>
+      <c r="J25" s="210" t="n"/>
+      <c r="K25" s="211" t="n"/>
+      <c r="L25" s="210" t="n"/>
+      <c r="M25" s="211" t="n"/>
+      <c r="N25" s="210" t="n"/>
       <c r="O25" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="P25" s="205" t="n"/>
+      <c r="P25" s="206" t="n"/>
       <c r="Q25" s="199" t="n"/>
       <c r="R25" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S25" s="206" t="n"/>
+      <c r="S25" s="207" t="n"/>
       <c r="T25" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING, 
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U25" s="206" t="n"/>
+      <c r="U25" s="207" t="n"/>
       <c r="V25" s="162" t="n">
         <v>3</v>
       </c>
@@ -6043,7 +6066,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X25" s="206" t="n"/>
+      <c r="X25" s="207" t="n"/>
       <c r="Y25" s="162" t="n">
         <v>5</v>
       </c>
@@ -6063,20 +6086,20 @@
       <c r="AL25" s="10" t="n"/>
     </row>
     <row r="26" ht="108" customFormat="1" customHeight="1" s="13">
-      <c r="B26" s="208" t="n"/>
-      <c r="C26" s="209" t="n"/>
-      <c r="D26" s="208" t="n"/>
-      <c r="E26" s="209" t="n"/>
-      <c r="F26" s="208" t="n"/>
-      <c r="G26" s="209" t="n"/>
-      <c r="H26" s="208" t="n"/>
-      <c r="I26" s="209" t="n"/>
-      <c r="J26" s="208" t="n"/>
-      <c r="K26" s="209" t="n"/>
-      <c r="L26" s="208" t="n"/>
-      <c r="M26" s="209" t="n"/>
-      <c r="N26" s="208" t="n"/>
-      <c r="O26" s="210" t="n"/>
+      <c r="B26" s="210" t="n"/>
+      <c r="C26" s="211" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="210" t="n"/>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="210" t="n"/>
+      <c r="I26" s="211" t="n"/>
+      <c r="J26" s="210" t="n"/>
+      <c r="K26" s="211" t="n"/>
+      <c r="L26" s="210" t="n"/>
+      <c r="M26" s="211" t="n"/>
+      <c r="N26" s="210" t="n"/>
+      <c r="O26" s="212" t="n"/>
       <c r="P26" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED-UNDER TORQUE</t>
@@ -6088,14 +6111,14 @@
           <t>SOS not followed by operator or CALIBRATION SET VALUE IS WRONG</t>
         </is>
       </c>
-      <c r="S26" s="206" t="n"/>
+      <c r="S26" s="207" t="n"/>
       <c r="T26" s="155" t="inlineStr">
         <is>
           <t>DEDICATED TOOLS FOR SPECIFIED TORQUE AND LABELS ON THE TOOL</t>
         </is>
       </c>
-      <c r="U26" s="206" t="n"/>
-      <c r="V26" s="210" t="n"/>
+      <c r="U26" s="207" t="n"/>
+      <c r="V26" s="212" t="n"/>
       <c r="W26" s="162" t="inlineStr">
         <is>
           <t>SELF CHECK,
@@ -6103,9 +6126,9 @@
 CALIBRATION RECORD</t>
         </is>
       </c>
-      <c r="X26" s="206" t="n"/>
-      <c r="Y26" s="210" t="n"/>
-      <c r="Z26" s="210" t="n"/>
+      <c r="X26" s="207" t="n"/>
+      <c r="Y26" s="212" t="n"/>
+      <c r="Z26" s="212" t="n"/>
       <c r="AA26" s="17" t="n"/>
       <c r="AB26" s="9" t="n"/>
       <c r="AC26" s="12" t="n"/>
@@ -6117,35 +6140,35 @@
       <c r="AL26" s="10" t="n"/>
     </row>
     <row r="27" ht="94.5" customFormat="1" customHeight="1" s="13">
-      <c r="B27" s="208" t="n"/>
-      <c r="C27" s="209" t="n"/>
-      <c r="D27" s="208" t="n"/>
-      <c r="E27" s="209" t="n"/>
-      <c r="F27" s="208" t="n"/>
-      <c r="G27" s="209" t="n"/>
-      <c r="H27" s="208" t="n"/>
-      <c r="I27" s="205" t="n"/>
+      <c r="B27" s="210" t="n"/>
+      <c r="C27" s="211" t="n"/>
+      <c r="D27" s="210" t="n"/>
+      <c r="E27" s="211" t="n"/>
+      <c r="F27" s="210" t="n"/>
+      <c r="G27" s="211" t="n"/>
+      <c r="H27" s="210" t="n"/>
+      <c r="I27" s="206" t="n"/>
       <c r="J27" s="199" t="n"/>
-      <c r="K27" s="209" t="n"/>
-      <c r="L27" s="208" t="n"/>
-      <c r="M27" s="205" t="n"/>
+      <c r="K27" s="211" t="n"/>
+      <c r="L27" s="210" t="n"/>
+      <c r="M27" s="206" t="n"/>
       <c r="N27" s="199" t="n"/>
-      <c r="O27" s="213" t="n"/>
+      <c r="O27" s="215" t="n"/>
       <c r="P27" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED - OVER TORQUE</t>
         </is>
       </c>
       <c r="Q27" s="201" t="n"/>
-      <c r="R27" s="205" t="n"/>
+      <c r="R27" s="206" t="n"/>
       <c r="S27" s="199" t="n"/>
-      <c r="T27" s="205" t="n"/>
+      <c r="T27" s="206" t="n"/>
       <c r="U27" s="199" t="n"/>
-      <c r="V27" s="213" t="n"/>
-      <c r="W27" s="205" t="n"/>
+      <c r="V27" s="215" t="n"/>
+      <c r="W27" s="206" t="n"/>
       <c r="X27" s="199" t="n"/>
-      <c r="Y27" s="213" t="n"/>
-      <c r="Z27" s="213" t="n"/>
+      <c r="Y27" s="215" t="n"/>
+      <c r="Z27" s="215" t="n"/>
       <c r="AA27" s="17" t="n"/>
       <c r="AB27" s="9" t="n"/>
       <c r="AC27" s="12" t="n"/>
@@ -6742,7 +6765,7 @@
       <c r="D14" s="195" t="n"/>
       <c r="E14" s="195" t="n"/>
       <c r="F14" s="199" t="n"/>
-      <c r="G14" s="205" t="n"/>
+      <c r="G14" s="206" t="n"/>
       <c r="H14" s="195" t="n"/>
       <c r="I14" s="195" t="n"/>
       <c r="J14" s="195" t="n"/>
@@ -6783,47 +6806,47 @@
 Name of Process</t>
         </is>
       </c>
-      <c r="B15" s="206" t="n"/>
+      <c r="B15" s="207" t="n"/>
       <c r="C15" s="96" t="inlineStr">
         <is>
           <t>2. Process Step Station No. and Name of
 Focus Element</t>
         </is>
       </c>
-      <c r="D15" s="206" t="n"/>
+      <c r="D15" s="207" t="n"/>
       <c r="E15" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Process Work Element </t>
         </is>
       </c>
-      <c r="F15" s="206" t="n"/>
+      <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
           <t>1. Function of the Process Item Function of System, Subsystem,
 Part Element or Process</t>
         </is>
       </c>
-      <c r="H15" s="206" t="n"/>
+      <c r="H15" s="207" t="n"/>
       <c r="I15" s="96" t="inlineStr">
         <is>
           <t>2. Function of the Process Step and Product Characteristic
 (Quantitative value is optional)</t>
         </is>
       </c>
-      <c r="J15" s="206" t="n"/>
+      <c r="J15" s="207" t="n"/>
       <c r="K15" s="99" t="inlineStr">
         <is>
           <t>3. Function of the Process Work Element and Process
 Characteristic</t>
         </is>
       </c>
-      <c r="L15" s="206" t="n"/>
+      <c r="L15" s="207" t="n"/>
       <c r="M15" s="91" t="inlineStr">
         <is>
           <t>1. Failure Effects (FE) to the Next Higher Level Element and/or End User</t>
         </is>
       </c>
-      <c r="N15" s="206" t="n"/>
+      <c r="N15" s="207" t="n"/>
       <c r="O15" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Severity (S) of FE
@@ -6836,19 +6859,19 @@
 Focus Element</t>
         </is>
       </c>
-      <c r="Q15" s="206" t="n"/>
+      <c r="Q15" s="207" t="n"/>
       <c r="R15" s="99" t="inlineStr">
         <is>
           <t>3. Failure Cause (FC) of the Work Element</t>
         </is>
       </c>
-      <c r="S15" s="206" t="n"/>
+      <c r="S15" s="207" t="n"/>
       <c r="T15" s="141" t="inlineStr">
         <is>
           <t>Current Prevention Control (PC) of FC</t>
         </is>
       </c>
-      <c r="U15" s="206" t="n"/>
+      <c r="U15" s="207" t="n"/>
       <c r="V15" s="109" t="inlineStr">
         <is>
           <t>Occurrence (O) of FC</t>
@@ -6859,7 +6882,7 @@
           <t>Current Detection Controls (DC) of FC or FM</t>
         </is>
       </c>
-      <c r="X15" s="206" t="n"/>
+      <c r="X15" s="207" t="n"/>
       <c r="Y15" s="109" t="inlineStr">
         <is>
           <t>Detection (D) of FC/FM</t>
@@ -6933,84 +6956,84 @@
       </c>
     </row>
     <row r="16" ht="22.5" customFormat="1" customHeight="1" s="6">
-      <c r="A16" s="207" t="n"/>
-      <c r="B16" s="208" t="n"/>
-      <c r="C16" s="209" t="n"/>
-      <c r="D16" s="208" t="n"/>
-      <c r="E16" s="209" t="n"/>
-      <c r="F16" s="208" t="n"/>
-      <c r="G16" s="209" t="n"/>
-      <c r="H16" s="208" t="n"/>
-      <c r="I16" s="209" t="n"/>
-      <c r="J16" s="208" t="n"/>
-      <c r="K16" s="209" t="n"/>
-      <c r="L16" s="208" t="n"/>
-      <c r="M16" s="207" t="n"/>
-      <c r="N16" s="208" t="n"/>
-      <c r="O16" s="210" t="n"/>
-      <c r="P16" s="209" t="n"/>
-      <c r="Q16" s="208" t="n"/>
-      <c r="R16" s="209" t="n"/>
-      <c r="S16" s="208" t="n"/>
-      <c r="T16" s="207" t="n"/>
-      <c r="U16" s="208" t="n"/>
-      <c r="V16" s="210" t="n"/>
-      <c r="W16" s="209" t="n"/>
-      <c r="X16" s="208" t="n"/>
-      <c r="Y16" s="210" t="n"/>
-      <c r="Z16" s="210" t="n"/>
-      <c r="AA16" s="211" t="n"/>
-      <c r="AB16" s="212" t="n"/>
-      <c r="AC16" s="210" t="n"/>
-      <c r="AD16" s="210" t="n"/>
-      <c r="AE16" s="210" t="n"/>
-      <c r="AF16" s="210" t="n"/>
-      <c r="AG16" s="210" t="n"/>
-      <c r="AH16" s="210" t="n"/>
-      <c r="AI16" s="210" t="n"/>
-      <c r="AJ16" s="210" t="n"/>
-      <c r="AK16" s="210" t="n"/>
-      <c r="AL16" s="211" t="n"/>
+      <c r="A16" s="209" t="n"/>
+      <c r="B16" s="210" t="n"/>
+      <c r="C16" s="211" t="n"/>
+      <c r="D16" s="210" t="n"/>
+      <c r="E16" s="211" t="n"/>
+      <c r="F16" s="210" t="n"/>
+      <c r="G16" s="211" t="n"/>
+      <c r="H16" s="210" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="210" t="n"/>
+      <c r="K16" s="211" t="n"/>
+      <c r="L16" s="210" t="n"/>
+      <c r="M16" s="209" t="n"/>
+      <c r="N16" s="210" t="n"/>
+      <c r="O16" s="212" t="n"/>
+      <c r="P16" s="211" t="n"/>
+      <c r="Q16" s="210" t="n"/>
+      <c r="R16" s="211" t="n"/>
+      <c r="S16" s="210" t="n"/>
+      <c r="T16" s="209" t="n"/>
+      <c r="U16" s="210" t="n"/>
+      <c r="V16" s="212" t="n"/>
+      <c r="W16" s="211" t="n"/>
+      <c r="X16" s="210" t="n"/>
+      <c r="Y16" s="212" t="n"/>
+      <c r="Z16" s="212" t="n"/>
+      <c r="AA16" s="213" t="n"/>
+      <c r="AB16" s="214" t="n"/>
+      <c r="AC16" s="212" t="n"/>
+      <c r="AD16" s="212" t="n"/>
+      <c r="AE16" s="212" t="n"/>
+      <c r="AF16" s="212" t="n"/>
+      <c r="AG16" s="212" t="n"/>
+      <c r="AH16" s="212" t="n"/>
+      <c r="AI16" s="212" t="n"/>
+      <c r="AJ16" s="212" t="n"/>
+      <c r="AK16" s="212" t="n"/>
+      <c r="AL16" s="213" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
       <c r="B17" s="199" t="n"/>
-      <c r="C17" s="205" t="n"/>
+      <c r="C17" s="206" t="n"/>
       <c r="D17" s="199" t="n"/>
-      <c r="E17" s="205" t="n"/>
+      <c r="E17" s="206" t="n"/>
       <c r="F17" s="199" t="n"/>
-      <c r="G17" s="205" t="n"/>
+      <c r="G17" s="206" t="n"/>
       <c r="H17" s="199" t="n"/>
-      <c r="I17" s="205" t="n"/>
+      <c r="I17" s="206" t="n"/>
       <c r="J17" s="199" t="n"/>
-      <c r="K17" s="205" t="n"/>
+      <c r="K17" s="206" t="n"/>
       <c r="L17" s="199" t="n"/>
       <c r="M17" s="198" t="n"/>
       <c r="N17" s="199" t="n"/>
-      <c r="O17" s="213" t="n"/>
-      <c r="P17" s="205" t="n"/>
+      <c r="O17" s="215" t="n"/>
+      <c r="P17" s="206" t="n"/>
       <c r="Q17" s="199" t="n"/>
-      <c r="R17" s="205" t="n"/>
+      <c r="R17" s="206" t="n"/>
       <c r="S17" s="199" t="n"/>
       <c r="T17" s="198" t="n"/>
       <c r="U17" s="199" t="n"/>
-      <c r="V17" s="213" t="n"/>
-      <c r="W17" s="205" t="n"/>
+      <c r="V17" s="215" t="n"/>
+      <c r="W17" s="206" t="n"/>
       <c r="X17" s="199" t="n"/>
-      <c r="Y17" s="213" t="n"/>
-      <c r="Z17" s="213" t="n"/>
-      <c r="AA17" s="214" t="n"/>
-      <c r="AB17" s="215" t="n"/>
-      <c r="AC17" s="213" t="n"/>
-      <c r="AD17" s="213" t="n"/>
-      <c r="AE17" s="213" t="n"/>
-      <c r="AF17" s="213" t="n"/>
-      <c r="AG17" s="213" t="n"/>
-      <c r="AH17" s="213" t="n"/>
-      <c r="AI17" s="213" t="n"/>
-      <c r="AJ17" s="213" t="n"/>
-      <c r="AK17" s="213" t="n"/>
-      <c r="AL17" s="214" t="n"/>
+      <c r="Y17" s="215" t="n"/>
+      <c r="Z17" s="215" t="n"/>
+      <c r="AA17" s="216" t="n"/>
+      <c r="AB17" s="217" t="n"/>
+      <c r="AC17" s="215" t="n"/>
+      <c r="AD17" s="215" t="n"/>
+      <c r="AE17" s="215" t="n"/>
+      <c r="AF17" s="215" t="n"/>
+      <c r="AG17" s="215" t="n"/>
+      <c r="AH17" s="215" t="n"/>
+      <c r="AI17" s="215" t="n"/>
+      <c r="AJ17" s="215" t="n"/>
+      <c r="AK17" s="215" t="n"/>
+      <c r="AL17" s="216" t="n"/>
     </row>
     <row r="18" ht="101.25" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -7018,8 +7041,8 @@
           <t>HEAD LAMP STAGE</t>
         </is>
       </c>
-      <c r="B18" s="206" t="n"/>
-      <c r="C18" s="216" t="inlineStr">
+      <c r="B18" s="207" t="n"/>
+      <c r="C18" s="218" t="inlineStr">
         <is>
           <t xml:space="preserve">Operation No: 
 Stage: 
@@ -7027,8 +7050,8 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="206" t="n"/>
-      <c r="E18" s="217" t="inlineStr">
+      <c r="D18" s="207" t="n"/>
+      <c r="E18" s="219" t="inlineStr">
         <is>
           <t>1 Man - Operator
 2.Machine-  
@@ -7041,8 +7064,8 @@
 6.Measurement- NA</t>
         </is>
       </c>
-      <c r="F18" s="206" t="n"/>
-      <c r="G18" s="218" t="inlineStr">
+      <c r="F18" s="207" t="n"/>
+      <c r="G18" s="220" t="inlineStr">
         <is>
           <t>Your Plant :
 1. Correct installation and positioning of the side seal during radiator assembly.
@@ -7054,14 +7077,14 @@
 3. Seal the joint between the radiator core and side tank to prevent coolant leakage</t>
         </is>
       </c>
-      <c r="H18" s="206" t="n"/>
+      <c r="H18" s="207" t="n"/>
       <c r="I18" s="162" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECTION OF SIDE SEAL </t>
         </is>
       </c>
-      <c r="J18" s="206" t="n"/>
-      <c r="K18" s="219" t="inlineStr">
+      <c r="J18" s="207" t="n"/>
+      <c r="K18" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Man: 
 1. GET THE SIDE SEAL FROM STORAGE BIN
@@ -7076,7 +7099,7 @@
 </t>
         </is>
       </c>
-      <c r="L18" s="206" t="n"/>
+      <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -7089,7 +7112,7 @@
 3. Customer dissatisfaction</t>
         </is>
       </c>
-      <c r="N18" s="206" t="n"/>
+      <c r="N18" s="207" t="n"/>
       <c r="O18" s="162" t="n">
         <v>5</v>
       </c>
@@ -7098,7 +7121,7 @@
           <t>WRONG PART SELECTION</t>
         </is>
       </c>
-      <c r="Q18" s="206" t="n"/>
+      <c r="Q18" s="207" t="n"/>
       <c r="R18" s="155" t="n"/>
       <c r="S18" s="201" t="n"/>
       <c r="T18" s="156" t="n"/>
@@ -7112,7 +7135,7 @@
 2. CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X18" s="206" t="n"/>
+      <c r="X18" s="207" t="n"/>
       <c r="Y18" s="162" t="n">
         <v>5</v>
       </c>
@@ -7132,45 +7155,45 @@
       <c r="AL18" s="35" t="n"/>
     </row>
     <row r="19" ht="184.5" customFormat="1" customHeight="1" s="8">
-      <c r="B19" s="208" t="n"/>
-      <c r="C19" s="209" t="n"/>
-      <c r="D19" s="208" t="n"/>
-      <c r="E19" s="209" t="n"/>
-      <c r="F19" s="208" t="n"/>
-      <c r="G19" s="209" t="n"/>
-      <c r="H19" s="208" t="n"/>
-      <c r="I19" s="205" t="n"/>
+      <c r="B19" s="210" t="n"/>
+      <c r="C19" s="211" t="n"/>
+      <c r="D19" s="210" t="n"/>
+      <c r="E19" s="211" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="211" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="206" t="n"/>
       <c r="J19" s="199" t="n"/>
-      <c r="K19" s="209" t="n"/>
-      <c r="L19" s="208" t="n"/>
-      <c r="M19" s="205" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="210" t="n"/>
+      <c r="M19" s="206" t="n"/>
       <c r="N19" s="199" t="n"/>
-      <c r="O19" s="213" t="n"/>
-      <c r="P19" s="205" t="n"/>
+      <c r="O19" s="215" t="n"/>
+      <c r="P19" s="206" t="n"/>
       <c r="Q19" s="199" t="n"/>
       <c r="R19" s="43" t="inlineStr">
         <is>
           <t>Sequence not followed by operator</t>
         </is>
       </c>
-      <c r="S19" s="206" t="n"/>
+      <c r="S19" s="207" t="n"/>
       <c r="T19" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING,
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U19" s="206" t="n"/>
-      <c r="V19" s="213" t="n"/>
+      <c r="U19" s="207" t="n"/>
+      <c r="V19" s="215" t="n"/>
       <c r="W19" s="45" t="inlineStr">
         <is>
           <t>1. SELF CHECK, 
 2. CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X19" s="206" t="n"/>
-      <c r="Y19" s="213" t="n"/>
-      <c r="Z19" s="213" t="n"/>
+      <c r="X19" s="207" t="n"/>
+      <c r="Y19" s="215" t="n"/>
+      <c r="Z19" s="215" t="n"/>
       <c r="AA19" s="162" t="n"/>
       <c r="AB19" s="162" t="n"/>
       <c r="AC19" s="45" t="n"/>
@@ -7182,18 +7205,18 @@
       <c r="AL19" s="35" t="n"/>
     </row>
     <row r="20" ht="107.45" customFormat="1" customHeight="1" s="8">
-      <c r="B20" s="208" t="n"/>
-      <c r="C20" s="209" t="n"/>
-      <c r="D20" s="208" t="n"/>
-      <c r="E20" s="209" t="n"/>
-      <c r="F20" s="208" t="n"/>
-      <c r="G20" s="209" t="n"/>
-      <c r="H20" s="208" t="n"/>
+      <c r="B20" s="210" t="n"/>
+      <c r="C20" s="211" t="n"/>
+      <c r="D20" s="210" t="n"/>
+      <c r="E20" s="211" t="n"/>
+      <c r="F20" s="210" t="n"/>
+      <c r="G20" s="211" t="n"/>
+      <c r="H20" s="210" t="n"/>
       <c r="I20" s="135" t="n"/>
       <c r="J20" s="136" t="n"/>
-      <c r="K20" s="209" t="n"/>
-      <c r="L20" s="208" t="n"/>
-      <c r="M20" s="221" t="inlineStr">
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="210" t="n"/>
+      <c r="M20" s="223" t="inlineStr">
         <is>
           <t>Your Plant:
 1. Cut, torn, pinched, or cracked seal
@@ -7206,14 +7229,14 @@
 3. Safety risk if overheating occurs during driving</t>
         </is>
       </c>
-      <c r="N20" s="206" t="n"/>
+      <c r="N20" s="207" t="n"/>
       <c r="O20" s="146" t="n"/>
       <c r="P20" s="162" t="inlineStr">
         <is>
           <t xml:space="preserve">IMPROPER LOCKING </t>
         </is>
       </c>
-      <c r="Q20" s="206" t="n"/>
+      <c r="Q20" s="207" t="n"/>
       <c r="R20" s="155" t="n"/>
       <c r="S20" s="201" t="n"/>
       <c r="T20" s="156" t="n"/>
@@ -7225,7 +7248,7 @@
 2. CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X20" s="206" t="n"/>
+      <c r="X20" s="207" t="n"/>
       <c r="Y20" s="146" t="n"/>
       <c r="Z20" s="146" t="n"/>
       <c r="AA20" s="162" t="n"/>
@@ -7239,41 +7262,41 @@
       <c r="AL20" s="35" t="n"/>
     </row>
     <row r="21" ht="186.95" customFormat="1" customHeight="1" s="14">
-      <c r="B21" s="208" t="n"/>
-      <c r="C21" s="209" t="n"/>
-      <c r="D21" s="208" t="n"/>
-      <c r="E21" s="209" t="n"/>
-      <c r="F21" s="208" t="n"/>
-      <c r="G21" s="209" t="n"/>
-      <c r="H21" s="208" t="n"/>
+      <c r="B21" s="210" t="n"/>
+      <c r="C21" s="211" t="n"/>
+      <c r="D21" s="210" t="n"/>
+      <c r="E21" s="211" t="n"/>
+      <c r="F21" s="210" t="n"/>
+      <c r="G21" s="211" t="n"/>
+      <c r="H21" s="210" t="n"/>
       <c r="I21" s="154" t="inlineStr">
         <is>
           <t>ALIGNMENT OF SIDE SEAL WITH BIW</t>
         </is>
       </c>
-      <c r="J21" s="206" t="n"/>
-      <c r="K21" s="209" t="n"/>
-      <c r="L21" s="208" t="n"/>
-      <c r="M21" s="209" t="n"/>
-      <c r="N21" s="208" t="n"/>
+      <c r="J21" s="207" t="n"/>
+      <c r="K21" s="211" t="n"/>
+      <c r="L21" s="210" t="n"/>
+      <c r="M21" s="211" t="n"/>
+      <c r="N21" s="210" t="n"/>
       <c r="O21" s="162" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="205" t="n"/>
+      <c r="P21" s="206" t="n"/>
       <c r="Q21" s="199" t="n"/>
       <c r="R21" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S21" s="206" t="n"/>
+      <c r="S21" s="207" t="n"/>
       <c r="T21" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING,
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U21" s="206" t="n"/>
+      <c r="U21" s="207" t="n"/>
       <c r="V21" s="162" t="n">
         <v>2</v>
       </c>
@@ -7283,7 +7306,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X21" s="206" t="n"/>
+      <c r="X21" s="207" t="n"/>
       <c r="Y21" s="162" t="n">
         <v>5</v>
       </c>
@@ -7306,40 +7329,40 @@
       <c r="AL21" s="10" t="n"/>
     </row>
     <row r="22" ht="108.75" customFormat="1" customHeight="1" s="14">
-      <c r="B22" s="208" t="n"/>
-      <c r="C22" s="209" t="n"/>
-      <c r="D22" s="208" t="n"/>
-      <c r="E22" s="209" t="n"/>
-      <c r="F22" s="208" t="n"/>
-      <c r="G22" s="209" t="n"/>
-      <c r="H22" s="208" t="n"/>
-      <c r="I22" s="209" t="n"/>
-      <c r="J22" s="208" t="n"/>
-      <c r="K22" s="209" t="n"/>
-      <c r="L22" s="208" t="n"/>
-      <c r="M22" s="209" t="n"/>
-      <c r="N22" s="208" t="n"/>
-      <c r="O22" s="210" t="n"/>
+      <c r="B22" s="210" t="n"/>
+      <c r="C22" s="211" t="n"/>
+      <c r="D22" s="210" t="n"/>
+      <c r="E22" s="211" t="n"/>
+      <c r="F22" s="210" t="n"/>
+      <c r="G22" s="211" t="n"/>
+      <c r="H22" s="210" t="n"/>
+      <c r="I22" s="211" t="n"/>
+      <c r="J22" s="210" t="n"/>
+      <c r="K22" s="211" t="n"/>
+      <c r="L22" s="210" t="n"/>
+      <c r="M22" s="211" t="n"/>
+      <c r="N22" s="210" t="n"/>
+      <c r="O22" s="212" t="n"/>
       <c r="P22" s="162" t="inlineStr">
         <is>
           <t>WRONG POSITIONING</t>
         </is>
       </c>
-      <c r="Q22" s="206" t="n"/>
+      <c r="Q22" s="207" t="n"/>
       <c r="R22" s="155" t="n"/>
       <c r="S22" s="201" t="n"/>
       <c r="T22" s="156" t="n"/>
       <c r="U22" s="201" t="n"/>
-      <c r="V22" s="210" t="n"/>
+      <c r="V22" s="212" t="n"/>
       <c r="W22" s="45" t="inlineStr">
         <is>
           <t>SELF CHECK WITH MARKING,
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X22" s="206" t="n"/>
-      <c r="Y22" s="210" t="n"/>
-      <c r="Z22" s="210" t="n"/>
+      <c r="X22" s="207" t="n"/>
+      <c r="Y22" s="212" t="n"/>
+      <c r="Z22" s="212" t="n"/>
       <c r="AA22" s="17" t="n"/>
       <c r="AB22" s="16" t="n"/>
       <c r="AC22" s="12" t="n"/>
@@ -7354,45 +7377,45 @@
       <c r="AL22" s="10" t="n"/>
     </row>
     <row r="23" ht="134.25" customFormat="1" customHeight="1" s="14">
-      <c r="B23" s="208" t="n"/>
-      <c r="C23" s="209" t="n"/>
-      <c r="D23" s="208" t="n"/>
-      <c r="E23" s="209" t="n"/>
-      <c r="F23" s="208" t="n"/>
-      <c r="G23" s="209" t="n"/>
-      <c r="H23" s="208" t="n"/>
-      <c r="I23" s="205" t="n"/>
+      <c r="B23" s="210" t="n"/>
+      <c r="C23" s="211" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="211" t="n"/>
+      <c r="F23" s="210" t="n"/>
+      <c r="G23" s="211" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="206" t="n"/>
       <c r="J23" s="199" t="n"/>
-      <c r="K23" s="209" t="n"/>
-      <c r="L23" s="208" t="n"/>
-      <c r="M23" s="205" t="n"/>
+      <c r="K23" s="211" t="n"/>
+      <c r="L23" s="210" t="n"/>
+      <c r="M23" s="206" t="n"/>
       <c r="N23" s="199" t="n"/>
-      <c r="O23" s="213" t="n"/>
-      <c r="P23" s="205" t="n"/>
+      <c r="O23" s="215" t="n"/>
+      <c r="P23" s="206" t="n"/>
       <c r="Q23" s="199" t="n"/>
       <c r="R23" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S23" s="206" t="n"/>
+      <c r="S23" s="207" t="n"/>
       <c r="T23" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING,
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U23" s="206" t="n"/>
-      <c r="V23" s="213" t="n"/>
+      <c r="U23" s="207" t="n"/>
+      <c r="V23" s="215" t="n"/>
       <c r="W23" s="45" t="inlineStr">
         <is>
           <t>SELF CHECK WITH MARKING,
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X23" s="206" t="n"/>
-      <c r="Y23" s="213" t="n"/>
-      <c r="Z23" s="213" t="n"/>
+      <c r="X23" s="207" t="n"/>
+      <c r="Y23" s="215" t="n"/>
+      <c r="Z23" s="215" t="n"/>
       <c r="AA23" s="15" t="n"/>
       <c r="AB23" s="16" t="n"/>
       <c r="AC23" s="12" t="n"/>
@@ -7407,21 +7430,21 @@
       <c r="AL23" s="10" t="n"/>
     </row>
     <row r="24" ht="92.25" customFormat="1" customHeight="1" s="14">
-      <c r="B24" s="208" t="n"/>
-      <c r="C24" s="209" t="n"/>
-      <c r="D24" s="208" t="n"/>
-      <c r="E24" s="209" t="n"/>
-      <c r="F24" s="208" t="n"/>
-      <c r="G24" s="209" t="n"/>
-      <c r="H24" s="208" t="n"/>
-      <c r="I24" s="223" t="inlineStr">
+      <c r="B24" s="210" t="n"/>
+      <c r="C24" s="211" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="211" t="n"/>
+      <c r="F24" s="210" t="n"/>
+      <c r="G24" s="211" t="n"/>
+      <c r="H24" s="210" t="n"/>
+      <c r="I24" s="225" t="inlineStr">
         <is>
           <t>PROPER TIGHTENING OF JOINT</t>
         </is>
       </c>
-      <c r="J24" s="206" t="n"/>
-      <c r="K24" s="209" t="n"/>
-      <c r="L24" s="208" t="n"/>
+      <c r="J24" s="207" t="n"/>
+      <c r="K24" s="211" t="n"/>
+      <c r="L24" s="210" t="n"/>
       <c r="M24" s="159" t="n"/>
       <c r="N24" s="160" t="n"/>
       <c r="O24" s="146" t="n"/>
@@ -7430,7 +7453,7 @@
           <t>OPERATOR FAILED TO FIT BOLTS</t>
         </is>
       </c>
-      <c r="Q24" s="206" t="n"/>
+      <c r="Q24" s="207" t="n"/>
       <c r="R24" s="155" t="n"/>
       <c r="S24" s="201" t="n"/>
       <c r="T24" s="156" t="n"/>
@@ -7442,7 +7465,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X24" s="206" t="n"/>
+      <c r="X24" s="207" t="n"/>
       <c r="Y24" s="146" t="n"/>
       <c r="Z24" s="152" t="n"/>
       <c r="AA24" s="15" t="n"/>
@@ -7459,17 +7482,17 @@
       <c r="AL24" s="10" t="n"/>
     </row>
     <row r="25" ht="135" customFormat="1" customHeight="1" s="13">
-      <c r="B25" s="208" t="n"/>
-      <c r="C25" s="209" t="n"/>
-      <c r="D25" s="208" t="n"/>
-      <c r="E25" s="209" t="n"/>
-      <c r="F25" s="208" t="n"/>
-      <c r="G25" s="209" t="n"/>
-      <c r="H25" s="208" t="n"/>
-      <c r="I25" s="209" t="n"/>
-      <c r="J25" s="208" t="n"/>
-      <c r="K25" s="209" t="n"/>
-      <c r="L25" s="208" t="n"/>
+      <c r="B25" s="210" t="n"/>
+      <c r="C25" s="211" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="211" t="n"/>
+      <c r="F25" s="210" t="n"/>
+      <c r="G25" s="211" t="n"/>
+      <c r="H25" s="210" t="n"/>
+      <c r="I25" s="211" t="n"/>
+      <c r="J25" s="210" t="n"/>
+      <c r="K25" s="211" t="n"/>
+      <c r="L25" s="210" t="n"/>
       <c r="M25" s="161" t="inlineStr">
         <is>
           <t>Your Plant:
@@ -7482,25 +7505,25 @@
 3. Rattling or vibration noise during driving</t>
         </is>
       </c>
-      <c r="N25" s="206" t="n"/>
+      <c r="N25" s="207" t="n"/>
       <c r="O25" s="162" t="n">
         <v>5</v>
       </c>
-      <c r="P25" s="205" t="n"/>
+      <c r="P25" s="206" t="n"/>
       <c r="Q25" s="199" t="n"/>
       <c r="R25" s="43" t="inlineStr">
         <is>
           <t>SOS not followed by operator</t>
         </is>
       </c>
-      <c r="S25" s="206" t="n"/>
+      <c r="S25" s="207" t="n"/>
       <c r="T25" s="43" t="inlineStr">
         <is>
           <t>OPERATOR TRAINING,
 WORK INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="U25" s="206" t="n"/>
+      <c r="U25" s="207" t="n"/>
       <c r="V25" s="162" t="n">
         <v>3</v>
       </c>
@@ -7510,7 +7533,7 @@
 CHECKMAN CHECKING</t>
         </is>
       </c>
-      <c r="X25" s="206" t="n"/>
+      <c r="X25" s="207" t="n"/>
       <c r="Y25" s="162" t="n">
         <v>5</v>
       </c>
@@ -7530,20 +7553,20 @@
       <c r="AL25" s="10" t="n"/>
     </row>
     <row r="26" ht="102" customFormat="1" customHeight="1" s="13">
-      <c r="B26" s="208" t="n"/>
-      <c r="C26" s="209" t="n"/>
-      <c r="D26" s="208" t="n"/>
-      <c r="E26" s="209" t="n"/>
-      <c r="F26" s="208" t="n"/>
-      <c r="G26" s="209" t="n"/>
-      <c r="H26" s="208" t="n"/>
-      <c r="I26" s="209" t="n"/>
-      <c r="J26" s="208" t="n"/>
-      <c r="K26" s="209" t="n"/>
-      <c r="L26" s="208" t="n"/>
-      <c r="M26" s="209" t="n"/>
-      <c r="N26" s="208" t="n"/>
-      <c r="O26" s="210" t="n"/>
+      <c r="B26" s="210" t="n"/>
+      <c r="C26" s="211" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="210" t="n"/>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="210" t="n"/>
+      <c r="I26" s="211" t="n"/>
+      <c r="J26" s="210" t="n"/>
+      <c r="K26" s="211" t="n"/>
+      <c r="L26" s="210" t="n"/>
+      <c r="M26" s="211" t="n"/>
+      <c r="N26" s="210" t="n"/>
+      <c r="O26" s="212" t="n"/>
       <c r="P26" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED-UNDER TORQUE</t>
@@ -7555,14 +7578,14 @@
           <t>SOS not followed by operator or tool calibration not done in intervals</t>
         </is>
       </c>
-      <c r="S26" s="206" t="n"/>
+      <c r="S26" s="207" t="n"/>
       <c r="T26" s="155" t="inlineStr">
         <is>
           <t>TORQUE CALIBRATION FREQUENCY TO BE DECIDE</t>
         </is>
       </c>
-      <c r="U26" s="206" t="n"/>
-      <c r="V26" s="210" t="n"/>
+      <c r="U26" s="207" t="n"/>
+      <c r="V26" s="212" t="n"/>
       <c r="W26" s="162" t="inlineStr">
         <is>
           <t>SELF CHECK WITH MARKING,
@@ -7570,9 +7593,9 @@
 CALIBRATION RECORD</t>
         </is>
       </c>
-      <c r="X26" s="206" t="n"/>
-      <c r="Y26" s="213" t="n"/>
-      <c r="Z26" s="213" t="n"/>
+      <c r="X26" s="207" t="n"/>
+      <c r="Y26" s="215" t="n"/>
+      <c r="Z26" s="215" t="n"/>
       <c r="AA26" s="17" t="n"/>
       <c r="AB26" s="9" t="n"/>
       <c r="AC26" s="12" t="n"/>
@@ -7584,32 +7607,32 @@
       <c r="AL26" s="10" t="n"/>
     </row>
     <row r="27" ht="114.6" customFormat="1" customHeight="1" s="13">
-      <c r="B27" s="208" t="n"/>
-      <c r="C27" s="209" t="n"/>
-      <c r="D27" s="208" t="n"/>
-      <c r="E27" s="209" t="n"/>
-      <c r="F27" s="208" t="n"/>
-      <c r="G27" s="209" t="n"/>
-      <c r="H27" s="208" t="n"/>
-      <c r="I27" s="205" t="n"/>
+      <c r="B27" s="210" t="n"/>
+      <c r="C27" s="211" t="n"/>
+      <c r="D27" s="210" t="n"/>
+      <c r="E27" s="211" t="n"/>
+      <c r="F27" s="210" t="n"/>
+      <c r="G27" s="211" t="n"/>
+      <c r="H27" s="210" t="n"/>
+      <c r="I27" s="206" t="n"/>
       <c r="J27" s="199" t="n"/>
-      <c r="K27" s="209" t="n"/>
-      <c r="L27" s="208" t="n"/>
-      <c r="M27" s="205" t="n"/>
+      <c r="K27" s="211" t="n"/>
+      <c r="L27" s="210" t="n"/>
+      <c r="M27" s="206" t="n"/>
       <c r="N27" s="199" t="n"/>
-      <c r="O27" s="213" t="n"/>
+      <c r="O27" s="215" t="n"/>
       <c r="P27" s="162" t="inlineStr">
         <is>
           <t>TORQUE NOT ACHIEVED - OVER TORQUE</t>
         </is>
       </c>
       <c r="Q27" s="201" t="n"/>
-      <c r="R27" s="205" t="n"/>
+      <c r="R27" s="206" t="n"/>
       <c r="S27" s="199" t="n"/>
-      <c r="T27" s="205" t="n"/>
+      <c r="T27" s="206" t="n"/>
       <c r="U27" s="199" t="n"/>
-      <c r="V27" s="213" t="n"/>
-      <c r="W27" s="205" t="n"/>
+      <c r="V27" s="215" t="n"/>
+      <c r="W27" s="206" t="n"/>
       <c r="X27" s="199" t="n"/>
       <c r="Y27" s="162" t="n"/>
       <c r="Z27" s="155" t="n"/>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
@@ -2470,20 +2470,20 @@
       <c r="AJ18" s="45" t="n"/>
       <c r="AK18" s="45" t="n"/>
       <c r="AL18" s="35" t="n"/>
-      <c r="AM18" t="n">
+      <c r="AM18" s="169" t="n">
         <v>8</v>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AN18" s="169" t="inlineStr">
         <is>
           <t>The End User effects list functional outcomes (no light or dim light) without any explicit safety or regulatory language; given the merged "scratch/damage" mode, the DAMAGE sub-mode can directly cause either total loss or degradation of the headlamp’s primary function, so the worst-case applicable definition is loss of primary function (8).</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AQ18" s="169" t="inlineStr">
         <is>
           <t>Add a mandatory barcode scan at the sequencing trolley that interlocks the station and blocks tool enable if the scanned headlamp PN/variant does not match the vehicle build sheet, preventing wrong-part selection/mix-up.</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
+      <c r="AR18" s="169" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. Scratch on head lamp; 2. Damage on head lamp. Cause/Mode mismatch: This Cause (wrong part/mix-up) does not physically produce a scratch/damage; it reads like the cause for installing the wrong headlamp variant rather than for scratching/damaging the part. Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: FITMENT IS NOT FIRM
  WRONG SELECTION OF HEAD LAMP
@@ -2577,20 +2577,20 @@
       <c r="AJ20" s="45" t="n"/>
       <c r="AK20" s="45" t="n"/>
       <c r="AL20" s="35" t="n"/>
-      <c r="AM20" t="n">
+      <c r="AM20" s="169" t="n">
         <v>8</v>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AN20" s="169" t="inlineStr">
         <is>
           <t>The End User effects list either a total loss of the headlamp function ('does not turn ON') or a degraded primary function ('dim light'), both directly plausible from wrong-part selection/mix-up; no safety or regulatory wording is stated. Per the table, these correspond to S=8 or S=7 respectively, with the row-level score set to the higher (8) due to merged/ambiguous mode effects.</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="AQ20" s="169" t="inlineStr">
         <is>
           <t>Add a scan-and-verify lockout at the pick/scan step so the headlamp barcode must match the vehicle’s model code and the line prevents installation if a wrong part is scanned.</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AR20" s="169" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. Fitment is not firm; 2. Wrong selection of head lamp (not as per model). Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
@@ -2698,20 +2698,20 @@
       <c r="AJ22" s="45" t="n"/>
       <c r="AK22" s="45" t="n"/>
       <c r="AL22" s="35" t="n"/>
-      <c r="AM22" t="n">
+      <c r="AM22" s="169" t="n">
         <v>10</v>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AN22" s="169" t="inlineStr">
         <is>
           <t>The End User effect list explicitly states 'Increased risk of accident', which is a plausible consequence of the headlamp not turning on or reduced visibility caused by improper/poor connector locking. Per the table, this affects safe operation of the vehicle, so Severity is 10.</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AQ22" s="169" t="inlineStr">
         <is>
           <t>Add a poka‑yoke for the headlamp connectors: a latch‑engagement sensor or pull‑back test with line interlock that prevents process completion if the connector is not fully seated and locked.</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AR22" s="169" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. IMPROPER LOCKING; 2. POOR LOCKING. AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
@@ -2829,20 +2829,20 @@
       <c r="AJ24" s="12" t="n"/>
       <c r="AK24" s="12" t="n"/>
       <c r="AL24" s="10" t="n"/>
-      <c r="AM24" t="n">
+      <c r="AM24" s="169" t="n">
         <v>10</v>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AN24" s="169" t="inlineStr">
         <is>
           <t>The End User effect explicitly states 'Increased risk of accident,' which is a direct and plausible consequence of a headlamp installed without required prefit bolts causing misalignment or compromised illumination. Per the Severity table, this affects safe operation of the vehicle, warranting a 10.</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="AQ24" s="169" t="inlineStr">
         <is>
           <t>Install a DC torque tool with bolt-count and torque OK interlock that prevents station completion unless all headlamp bolts are started and torqued to 6 Nm per the SOS.</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AR24" s="169" t="inlineStr">
         <is>
           <t>AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
@@ -2956,20 +2956,20 @@
       <c r="AJ26" s="12" t="n"/>
       <c r="AK26" s="12" t="n"/>
       <c r="AL26" s="10" t="n"/>
-      <c r="AM26" t="n">
+      <c r="AM26" s="169" t="n">
         <v>4</v>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AN26" s="169" t="inlineStr">
         <is>
           <t>Among the listed End User effects, the only direct outcome of 'failed to fit screws/not maintained gap' is 'rattling or vibration noise during driving', which falls under very objectionable sound/vibration. The more severe-sounding effects (lens crack, bulb burnout, water ingress) require additional unstated failures and are therefore indirect for this mode/cause.</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AQ26" s="169" t="inlineStr">
         <is>
           <t>Add an in-station fixture with hard locators and an interlocked gap/fastener verification (camera or go/no-go gauge plus screw-counting torque tool) that blocks OK-to-ship unless uniform gaps are met and all screws are installed/torqued.</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AR26" s="169" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. Failed to fit screws; 2. Not maintained gap. Cause/Mode mismatch: The stated Cause addresses only non-uniform gaps to the fender; it does not explain the 'failed to fit screws' portion of the Failure Mode.</t>
         </is>
@@ -3090,20 +3090,20 @@
       <c r="AJ28" s="12" t="n"/>
       <c r="AK28" s="12" t="n"/>
       <c r="AL28" s="10" t="n"/>
-      <c r="AM28" t="n">
+      <c r="AM28" s="169" t="n">
         <v>4</v>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AN28" s="169" t="inlineStr">
         <is>
           <t>The direct customer-facing outcome of an under-torqued headlamp mount is rattle/vibration noise while driving, which fits the table’s NVH category. This is reasonably treated as very objectionable NVH, aligning with Severity 4.</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="AQ28" s="169" t="inlineStr">
         <is>
           <t>Install a torque-controlled, calibrated electric driver programmed to 6 Nm with OK/NOK lockout to prevent under-torque from operator mistake, wrong tool use, or miscalibration.</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AR28" s="169" t="inlineStr">
         <is>
           <t>Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
@@ -3148,20 +3148,20 @@
       <c r="AJ29" s="12" t="n"/>
       <c r="AK29" s="12" t="n"/>
       <c r="AL29" s="10" t="n"/>
-      <c r="AM29" t="n">
+      <c r="AM29" s="169" t="n">
         <v>4</v>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AN29" s="169" t="inlineStr">
         <is>
           <t>The direct customer outcomes of this torque error are a cracked/broken lens (over‑torque) or rattling/vibration noise (under‑torque), which are NVH/appearance issues; there is no explicit accident/injury or regulatory noncompliance stated, and loss/degradation of illumination is not directly attributed to this torque error in the listed effects.</t>
         </is>
       </c>
-      <c r="AQ29" t="inlineStr">
+      <c r="AQ29" s="169" t="inlineStr">
         <is>
           <t>Install a DC torque tool programmed to 6 Nm with barcode-linked job selection and OK/NOK lockout so the station cannot proceed if the specified torque is not achieved, preventing wrong tool use and calibration drift from producing under/over‑torque.</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AR29" s="169" t="inlineStr">
         <is>
           <t>Merged failure mode: 1. Under‑torque (torque not achieved); 2. Over‑torque. Ambiguous - plausible severities: S4 (Lens cracked or broken); S4 (Rattling or vibration noise during driving). Suggested value is the worst case; review before finalizing. Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="30" customFormat="1" s="18"/>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="152">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="K18:L29"/>
     <mergeCell ref="I24:J25"/>
@@ -3186,6 +3186,7 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G13:L14"/>
+    <mergeCell ref="AR24:AR25"/>
     <mergeCell ref="K9:T9"/>
     <mergeCell ref="K5:T5"/>
     <mergeCell ref="T28:U29"/>
@@ -3193,11 +3194,14 @@
     <mergeCell ref="K11:T11"/>
     <mergeCell ref="I3:T4"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="AM22:AM23"/>
     <mergeCell ref="K12:T12"/>
     <mergeCell ref="V15:V17"/>
     <mergeCell ref="Y18:Y21"/>
     <mergeCell ref="R18:S18"/>
+    <mergeCell ref="AM18:AM19"/>
     <mergeCell ref="T27:U27"/>
+    <mergeCell ref="AR18:AR19"/>
     <mergeCell ref="AP15:AP17"/>
     <mergeCell ref="K8:T8"/>
     <mergeCell ref="AR15:AR17"/>
@@ -3205,19 +3209,26 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="M22:N25"/>
     <mergeCell ref="T24:U24"/>
+    <mergeCell ref="AQ20:AQ21"/>
     <mergeCell ref="T15:U17"/>
+    <mergeCell ref="AN24:AN25"/>
     <mergeCell ref="K7:T7"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="AN20:AN21"/>
+    <mergeCell ref="AQ22:AQ23"/>
+    <mergeCell ref="AN26:AN27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="Z18:Z21"/>
     <mergeCell ref="T25:U25"/>
+    <mergeCell ref="AN22:AN23"/>
     <mergeCell ref="P18:Q19"/>
     <mergeCell ref="AQ15:AQ17"/>
     <mergeCell ref="Y23:Y25"/>
     <mergeCell ref="Z27:Z29"/>
+    <mergeCell ref="AR20:AR21"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="M15:N17"/>
     <mergeCell ref="G18:H29"/>
@@ -3233,6 +3244,7 @@
     <mergeCell ref="AC15:AC17"/>
     <mergeCell ref="R28:S29"/>
     <mergeCell ref="I26:J27"/>
+    <mergeCell ref="AQ24:AQ25"/>
     <mergeCell ref="AD15:AD17"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="A7:C7"/>
@@ -3241,6 +3253,7 @@
     <mergeCell ref="A13:F14"/>
     <mergeCell ref="I28:J29"/>
     <mergeCell ref="AF15:AF17"/>
+    <mergeCell ref="AQ26:AQ27"/>
     <mergeCell ref="P15:Q17"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="AH15:AH17"/>
@@ -3249,20 +3262,24 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="O18:O21"/>
     <mergeCell ref="M18:N21"/>
+    <mergeCell ref="AN18:AN19"/>
     <mergeCell ref="A1:R2"/>
     <mergeCell ref="AL15:AL17"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="R27:S27"/>
     <mergeCell ref="R20:S20"/>
+    <mergeCell ref="AM20:AM21"/>
     <mergeCell ref="W28:X29"/>
     <mergeCell ref="P20:Q21"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="P22:Q23"/>
+    <mergeCell ref="AR22:AR23"/>
     <mergeCell ref="V18:V21"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="AO15:AO17"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="V27:V29"/>
+    <mergeCell ref="AM26:AM27"/>
     <mergeCell ref="A3:H4"/>
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="I15:J17"/>
@@ -3281,11 +3298,13 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="R24:S24"/>
+    <mergeCell ref="AM24:AM25"/>
     <mergeCell ref="M13:S14"/>
     <mergeCell ref="P24:Q25"/>
     <mergeCell ref="AM13:AR14"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="Z15:Z17"/>
+    <mergeCell ref="AQ18:AQ19"/>
     <mergeCell ref="AB15:AB17"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="T21:U21"/>
@@ -3300,6 +3319,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="T23:U23"/>
     <mergeCell ref="D10:F10"/>
+    <mergeCell ref="AR26:AR27"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="T18:U18"/>
   </mergeCells>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions.xlsx
@@ -1216,7 +1216,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1607,6 +1607,12 @@
   <cols>
     <col width="9.85546875" customWidth="1" min="1" max="1"/>
     <col width="12.5703125" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="32" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="32" customWidth="1" min="42" max="42"/>
+    <col width="38" customWidth="1" min="43" max="43"/>
+    <col width="55" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="1">
